--- a/Data/FlightPlan/FPL_16OCT26.xlsx
+++ b/Data/FlightPlan/FPL_16OCT26.xlsx
@@ -209,6 +209,12 @@
     <t>13:20</t>
   </si>
   <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>03:20</t>
+  </si>
+  <si>
     <t>CXR</t>
   </si>
   <si>
@@ -218,6 +224,12 @@
     <t>19:05</t>
   </si>
   <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
     <t>VN-A500</t>
   </si>
   <si>
@@ -353,9 +365,6 @@
     <t>17:05</t>
   </si>
   <si>
-    <t>18:30</t>
-  </si>
-  <si>
     <t>20:40</t>
   </si>
   <si>
@@ -869,9 +878,6 @@
     <t>VN-A639</t>
   </si>
   <si>
-    <t>06:05</t>
-  </si>
-  <si>
     <t>08:15</t>
   </si>
   <si>
@@ -965,120 +971,120 @@
     <t>VN-A650</t>
   </si>
   <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
     <t>08:25</t>
   </si>
   <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
     <t>PKX</t>
   </si>
   <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
     <t>VN-A670</t>
   </si>
   <si>
@@ -1193,7 +1199,7 @@
     <t>Total Record(s): 343</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 15, 2026 22:38</t>
+    <t xml:space="preserve">Generated on  Oct 16, 2026 01:38</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2392,9 +2398,13 @@
       <c t="s" r="J28" s="7">
         <v>65</v>
       </c>
-      <c r="K28" s="7"/>
+      <c t="s" r="K28" s="7">
+        <v>66</v>
+      </c>
       <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
+      <c t="s" r="M28" s="7">
+        <v>67</v>
+      </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c t="s" r="A29" s="6">
@@ -2417,17 +2427,21 @@
         <v>34</v>
       </c>
       <c t="s" r="H29" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>68</v>
-      </c>
-      <c r="K29" s="7"/>
+        <v>70</v>
+      </c>
+      <c t="s" r="K29" s="7">
+        <v>71</v>
+      </c>
       <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
+      <c t="s" r="M29" s="7">
+        <v>72</v>
+      </c>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="6"/>
@@ -2456,7 +2470,7 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
@@ -2465,13 +2479,13 @@
         <v>16</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2489,22 +2503,22 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H32" s="8">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2522,22 +2536,22 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G33" s="8">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c t="s" r="H33" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I33" s="7">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2570,7 +2584,7 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
@@ -2579,13 +2593,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H35" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2603,22 +2617,22 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G36" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="H36" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2636,7 +2650,7 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
@@ -2648,10 +2662,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2684,7 +2698,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2693,10 +2707,10 @@
         <v>54</v>
       </c>
       <c t="s" r="H39" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>49</v>
@@ -2717,22 +2731,22 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G40" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="H40" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2750,7 +2764,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2762,10 +2776,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
@@ -2783,7 +2797,7 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
@@ -2792,13 +2806,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H42" s="8">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
@@ -2827,11 +2841,11 @@
         <v>2869</v>
       </c>
       <c t="s" r="C44" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
@@ -2840,13 +2854,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H44" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -2864,22 +2878,22 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G45" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H45" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -2897,7 +2911,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -2906,13 +2920,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -2930,22 +2944,22 @@
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K47" s="7"/>
       <c r="L47" s="7"/>
@@ -2978,7 +2992,7 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
@@ -2987,13 +3001,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H49" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3011,22 +3025,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G50" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="H50" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3044,7 +3058,7 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
@@ -3053,13 +3067,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H51" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3077,19 +3091,19 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G52" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H52" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="J52" s="7">
         <v>55</v>
@@ -3110,7 +3124,7 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
@@ -3122,7 +3136,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I53" s="7">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c t="s" r="J53" s="7">
         <v>50</v>
@@ -3143,7 +3157,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3155,10 +3169,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3176,7 +3190,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3188,10 +3202,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3209,7 +3223,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3221,10 +3235,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3257,7 +3271,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3266,13 +3280,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3290,19 +3304,19 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J59" s="7">
         <v>25</v>
@@ -3323,7 +3337,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3332,13 +3346,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3356,22 +3370,22 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G61" s="8">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3404,7 +3418,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3413,13 +3427,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H63" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J63" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3437,22 +3451,22 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G64" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H64" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3470,7 +3484,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3482,7 +3496,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>38</v>
@@ -3503,7 +3517,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3515,10 +3529,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3536,7 +3550,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -3545,13 +3559,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3569,22 +3583,22 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3602,7 +3616,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -3614,10 +3628,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3650,7 +3664,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -3659,13 +3673,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H71" s="8">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3683,22 +3697,22 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="H72" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3716,7 +3730,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -3725,13 +3739,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -3749,19 +3763,19 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J74" s="7">
         <v>38</v>
@@ -3782,7 +3796,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -3794,10 +3808,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
@@ -3815,7 +3829,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3827,10 +3841,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -3848,7 +3862,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -3860,10 +3874,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -3881,7 +3895,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -3890,10 +3904,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c t="s" r="J78" s="7">
         <v>48</v>
@@ -3929,7 +3943,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -3938,13 +3952,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -3962,13 +3976,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>54</v>
@@ -3977,7 +3991,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -3995,7 +4009,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4007,10 +4021,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4028,7 +4042,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4040,10 +4054,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4061,7 +4075,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4073,10 +4087,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4109,7 +4123,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4118,13 +4132,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4142,22 +4156,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4175,7 +4189,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4184,13 +4198,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4208,22 +4222,22 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4256,7 +4270,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4265,13 +4279,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4289,19 +4303,19 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J92" s="7">
         <v>38</v>
@@ -4322,7 +4336,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4331,10 +4345,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>23</v>
@@ -4355,22 +4369,22 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4403,7 +4417,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4415,10 +4429,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4436,7 +4450,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4445,13 +4459,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -4469,22 +4483,22 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G98" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H98" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4502,7 +4516,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4514,7 +4528,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>51</v>
@@ -4535,7 +4549,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4547,10 +4561,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4568,7 +4582,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -4616,7 +4630,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4628,10 +4642,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4649,7 +4663,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4661,7 +4675,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>21</v>
@@ -4682,7 +4696,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4694,10 +4708,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -4715,7 +4729,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4730,7 +4744,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -4748,7 +4762,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4757,13 +4771,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4781,22 +4795,22 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4829,7 +4843,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -4838,10 +4852,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H110" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>21</v>
@@ -4862,19 +4876,19 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H111" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J111" s="7">
         <v>55</v>
@@ -4895,7 +4909,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -4904,13 +4918,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4928,13 +4942,13 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>34</v>
@@ -4961,7 +4975,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -4973,10 +4987,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -4994,7 +5008,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5006,10 +5020,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5042,7 +5056,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5051,13 +5065,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5075,22 +5089,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5108,7 +5122,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5117,13 +5131,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5141,22 +5155,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5174,7 +5188,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5183,13 +5197,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5207,19 +5221,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>58</v>
@@ -5255,7 +5269,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5267,10 +5281,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -5288,7 +5302,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5300,7 +5314,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>49</v>
@@ -5336,7 +5350,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5348,10 +5362,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5369,7 +5383,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5381,10 +5395,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -5402,7 +5416,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5411,13 +5425,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I129" s="7">
         <v>51</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5435,22 +5449,22 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5483,7 +5497,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5492,13 +5506,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5512,26 +5526,26 @@
         <v>5068</v>
       </c>
       <c t="s" r="C133" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -5545,11 +5559,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C134" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5558,13 +5572,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H134" s="8">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="I134" s="7">
         <v>39</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
@@ -5578,26 +5592,26 @@
         <v>5069</v>
       </c>
       <c t="s" r="C135" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G135" s="8">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c t="s" r="H135" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5630,7 +5644,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5639,13 +5653,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5663,22 +5677,22 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5696,7 +5710,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5705,13 +5719,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H139" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5729,19 +5743,19 @@
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J140" s="7">
         <v>26</v>
@@ -5773,26 +5787,26 @@
         <v>7615</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5806,11 +5820,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5819,13 +5833,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H143" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5839,23 +5853,23 @@
         <v>7706</v>
       </c>
       <c t="s" r="C144" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G144" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H144" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>52</v>
@@ -5872,11 +5886,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C145" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5885,13 +5899,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5924,7 +5938,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -5936,10 +5950,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -5957,7 +5971,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -5969,10 +5983,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -5990,7 +6004,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6002,10 +6016,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6023,7 +6037,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6035,10 +6049,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6056,7 +6070,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6068,10 +6082,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6104,7 +6118,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6116,10 +6130,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6137,7 +6151,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6149,10 +6163,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6170,22 +6184,22 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
+        <v>241</v>
+      </c>
+      <c r="F155" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G155" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="H155" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I155" s="7">
         <v>238</v>
       </c>
-      <c r="F155" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G155" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H155" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="I155" s="7">
-        <v>235</v>
-      </c>
       <c t="s" r="J155" s="7">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="K155" s="7"/>
       <c r="L155" s="7"/>
@@ -6203,7 +6217,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6218,7 +6232,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6251,22 +6265,22 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6284,7 +6298,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6293,13 +6307,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H159" s="8">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6332,7 +6346,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6344,10 +6358,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6365,7 +6379,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6374,13 +6388,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6398,22 +6412,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6431,7 +6445,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6440,7 +6454,7 @@
         <v>54</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>22</v>
@@ -6464,22 +6478,22 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H165" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6512,7 +6526,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6524,10 +6538,10 @@
         <v>37</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6545,7 +6559,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6557,10 +6571,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6578,7 +6592,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6593,7 +6607,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6611,7 +6625,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6623,10 +6637,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6644,7 +6658,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6656,10 +6670,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -6692,7 +6706,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6701,13 +6715,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6725,22 +6739,22 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -6758,7 +6772,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6767,13 +6781,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6791,22 +6805,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6824,7 +6838,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6833,13 +6847,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H177" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6857,22 +6871,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -6905,7 +6919,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -6917,10 +6931,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -6938,7 +6952,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -6947,13 +6961,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -6971,22 +6985,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H182" s="8">
         <v>29</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7019,7 +7033,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7034,7 +7048,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7052,7 +7066,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7061,13 +7075,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7085,22 +7099,22 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7118,7 +7132,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7130,10 +7144,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7151,7 +7165,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7163,17 +7177,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c t="s" r="K188" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7188,7 +7202,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7200,7 +7214,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>40</v>
@@ -7236,7 +7250,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7245,13 +7259,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7269,19 +7283,19 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>50</v>
@@ -7302,7 +7316,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7311,13 +7325,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7335,22 +7349,22 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7368,7 +7382,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7380,10 +7394,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7401,7 +7415,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7413,10 +7427,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7449,7 +7463,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7458,13 +7472,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="I198" s="7">
         <v>48</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7482,22 +7496,22 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7515,7 +7529,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7524,13 +7538,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7548,22 +7562,22 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7596,7 +7610,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7605,13 +7619,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7629,22 +7643,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7662,22 +7676,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7695,22 +7709,22 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -7728,7 +7742,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7737,13 +7751,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7761,22 +7775,22 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="H208" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7794,7 +7808,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7806,10 +7820,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7827,7 +7841,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7839,10 +7853,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7875,7 +7889,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7887,10 +7901,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>286</v>
+        <v>72</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7908,7 +7922,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -7920,10 +7934,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -7941,7 +7955,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -7950,13 +7964,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -7974,22 +7988,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8007,22 +8021,22 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
@@ -8040,22 +8054,22 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8088,7 +8102,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8097,13 +8111,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8121,22 +8135,22 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8154,7 +8168,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8163,13 +8177,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
@@ -8187,13 +8201,13 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>54</v>
@@ -8202,7 +8216,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
@@ -8235,7 +8249,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8247,10 +8261,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8268,7 +8282,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8280,17 +8294,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8305,7 +8319,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8320,14 +8334,14 @@
         <v>35</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c t="s" r="K226" s="7">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8342,7 +8356,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8354,17 +8368,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c t="s" r="K227" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -8379,7 +8393,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8391,10 +8405,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8412,7 +8426,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8421,13 +8435,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8445,19 +8459,19 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>26</v>
@@ -8478,7 +8492,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8487,13 +8501,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8511,22 +8525,22 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H232" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8559,7 +8573,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8568,13 +8582,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8592,13 +8606,13 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>54</v>
@@ -8607,7 +8621,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8625,7 +8639,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8634,13 +8648,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -8658,22 +8672,22 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8706,22 +8720,22 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8739,7 +8753,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8748,10 +8762,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c t="s" r="J240" s="7">
         <v>40</v>
@@ -8772,22 +8786,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -8805,7 +8819,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -8817,10 +8831,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8853,7 +8867,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -8862,13 +8876,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H244" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8886,13 +8900,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>17</v>
@@ -8901,7 +8915,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -8934,7 +8948,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -8946,10 +8960,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -8967,7 +8981,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -8976,13 +8990,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9000,22 +9014,22 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
@@ -9033,7 +9047,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9045,7 +9059,7 @@
         <v>47</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>48</v>
@@ -9081,22 +9095,22 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9114,7 +9128,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9129,7 +9143,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9147,7 +9161,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9162,7 +9176,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9180,7 +9194,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9192,10 +9206,10 @@
         <v>29</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9228,7 +9242,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9240,10 +9254,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9261,7 +9275,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9270,13 +9284,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9294,22 +9308,22 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9342,7 +9356,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9354,7 +9368,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>38</v>
@@ -9375,7 +9389,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9390,7 +9404,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9408,7 +9422,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9417,13 +9431,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9441,22 +9455,22 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9482,14 +9496,14 @@
         <v>13</v>
       </c>
       <c r="B266" s="7">
-        <v>382</v>
+        <v>1372</v>
       </c>
       <c t="s" r="C266" s="7">
         <v>14</v>
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9498,13 +9512,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>141</v>
+        <v>320</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>289</v>
+        <v>110</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9515,29 +9529,29 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>383</v>
+        <v>1373</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>141</v>
+        <v>320</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>319</v>
+        <v>129</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>269</v>
+        <v>322</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9555,7 +9569,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9567,10 +9581,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9588,7 +9602,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -9600,10 +9614,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9621,7 +9635,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9633,10 +9647,10 @@
         <v>320</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9654,7 +9668,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -9666,10 +9680,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9687,7 +9701,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F272" s="7">
         <v>320</v>
@@ -9699,10 +9713,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9735,7 +9749,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9744,13 +9758,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9768,22 +9782,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9801,7 +9815,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9810,13 +9824,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="I276" s="7">
         <v>24</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -9834,13 +9848,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>54</v>
@@ -9849,7 +9863,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -9867,7 +9881,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9879,7 +9893,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>28</v>
@@ -9915,7 +9929,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -9924,13 +9938,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -9948,22 +9962,22 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -9989,14 +10003,14 @@
         <v>13</v>
       </c>
       <c r="B283" s="7">
-        <v>1372</v>
+        <v>122</v>
       </c>
       <c t="s" r="C283" s="7">
         <v>14</v>
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10005,13 +10019,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>106</v>
+        <v>333</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10022,29 +10036,29 @@
         <v>13</v>
       </c>
       <c r="B284" s="7">
-        <v>1373</v>
+        <v>463</v>
       </c>
       <c t="s" r="C284" s="7">
         <v>14</v>
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>126</v>
+        <v>185</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>330</v>
+        <v>103</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10055,29 +10069,29 @@
         <v>13</v>
       </c>
       <c r="B285" s="7">
-        <v>374</v>
+        <v>464</v>
       </c>
       <c t="s" r="C285" s="7">
         <v>14</v>
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>54</v>
+        <v>131</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>274</v>
+        <v>124</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>200</v>
+        <v>116</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10088,29 +10102,29 @@
         <v>13</v>
       </c>
       <c r="B286" s="7">
-        <v>375</v>
+        <v>567</v>
       </c>
       <c t="s" r="C286" s="7">
         <v>14</v>
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>320</v>
+        <v>34</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>265</v>
+        <v>242</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>266</v>
+        <v>163</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10121,29 +10135,29 @@
         <v>13</v>
       </c>
       <c r="B287" s="7">
-        <v>3948</v>
+        <v>568</v>
       </c>
       <c t="s" r="C287" s="7">
         <v>14</v>
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>54</v>
+        <v>199</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>240</v>
+        <v>278</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>167</v>
+        <v>238</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10151,81 +10165,81 @@
     </row>
     <row r="288" ht="14.25" customHeight="1">
       <c t="s" r="A288" s="6">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B288" s="7">
-        <v>3949</v>
+        <v>7238</v>
       </c>
       <c t="s" r="C288" s="7">
         <v>14</v>
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>331</v>
+        <v>34</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>54</v>
+        <v>334</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c r="M288" s="7"/>
     </row>
     <row r="289" ht="14.25" customHeight="1">
-      <c r="A289" s="6"/>
-      <c r="B289" s="7"/>
-      <c r="C289" s="7"/>
+      <c t="s" r="A289" s="6">
+        <v>42</v>
+      </c>
+      <c r="B289" s="7">
+        <v>7239</v>
+      </c>
+      <c t="s" r="C289" s="7">
+        <v>14</v>
+      </c>
       <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="7"/>
-      <c r="G289" s="8"/>
-      <c r="H289" s="8"/>
-      <c r="I289" s="7"/>
-      <c r="J289" s="7"/>
+      <c t="s" r="E289" s="7">
+        <v>331</v>
+      </c>
+      <c r="F289" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G289" s="8">
+        <v>334</v>
+      </c>
+      <c t="s" r="H289" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I289" s="7">
+        <v>336</v>
+      </c>
+      <c t="s" r="J289" s="7">
+        <v>337</v>
+      </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
       <c r="M289" s="7"/>
     </row>
     <row r="290" ht="15" customHeight="1">
-      <c t="s" r="A290" s="6">
-        <v>13</v>
-      </c>
-      <c r="B290" s="7">
-        <v>339</v>
-      </c>
-      <c t="s" r="C290" s="7">
-        <v>14</v>
-      </c>
+      <c r="A290" s="6"/>
+      <c r="B290" s="7"/>
+      <c r="C290" s="7"/>
       <c r="D290" s="7"/>
-      <c t="s" r="E290" s="7">
-        <v>332</v>
-      </c>
-      <c r="F290" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G290" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="H290" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I290" s="7">
-        <v>84</v>
-      </c>
-      <c t="s" r="J290" s="7">
-        <v>250</v>
-      </c>
+      <c r="E290" s="7"/>
+      <c r="F290" s="7"/>
+      <c r="G290" s="8"/>
+      <c r="H290" s="8"/>
+      <c r="I290" s="7"/>
+      <c r="J290" s="7"/>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c r="M290" s="7"/>
@@ -10235,29 +10249,29 @@
         <v>13</v>
       </c>
       <c r="B291" s="7">
-        <v>718</v>
+        <v>339</v>
       </c>
       <c t="s" r="C291" s="7">
         <v>14</v>
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>207</v>
+        <v>88</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>269</v>
+        <v>253</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10268,29 +10282,29 @@
         <v>13</v>
       </c>
       <c r="B292" s="7">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c t="s" r="C292" s="7">
         <v>14</v>
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H292" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H292" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I292" s="7">
-        <v>131</v>
+        <v>210</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>299</v>
+        <v>272</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10301,29 +10315,29 @@
         <v>13</v>
       </c>
       <c r="B293" s="7">
-        <v>452</v>
+        <v>719</v>
       </c>
       <c t="s" r="C293" s="7">
         <v>14</v>
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>266</v>
+        <v>301</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10334,29 +10348,29 @@
         <v>13</v>
       </c>
       <c r="B294" s="7">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c t="s" r="C294" s="7">
         <v>14</v>
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>234</v>
+        <v>125</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>223</v>
+        <v>269</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10367,78 +10381,78 @@
         <v>13</v>
       </c>
       <c r="B295" s="7">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c t="s" r="C295" s="7">
         <v>14</v>
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>96</v>
+        <v>34</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>74</v>
+        <v>237</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>283</v>
+        <v>226</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
       <c r="M295" s="7"/>
     </row>
     <row r="296" ht="14.25" customHeight="1">
-      <c r="A296" s="6"/>
-      <c r="B296" s="7"/>
-      <c r="C296" s="7"/>
+      <c t="s" r="A296" s="6">
+        <v>13</v>
+      </c>
+      <c r="B296" s="7">
+        <v>442</v>
+      </c>
+      <c t="s" r="C296" s="7">
+        <v>14</v>
+      </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="7"/>
-      <c r="G296" s="8"/>
-      <c r="H296" s="8"/>
-      <c r="I296" s="7"/>
-      <c r="J296" s="7"/>
+      <c t="s" r="E296" s="7">
+        <v>338</v>
+      </c>
+      <c r="F296" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G296" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H296" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I296" s="7">
+        <v>78</v>
+      </c>
+      <c t="s" r="J296" s="7">
+        <v>286</v>
+      </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c r="M296" s="7"/>
     </row>
     <row r="297" ht="14.25" customHeight="1">
-      <c t="s" r="A297" s="6">
-        <v>13</v>
-      </c>
-      <c r="B297" s="7">
-        <v>403</v>
-      </c>
-      <c t="s" r="C297" s="7">
-        <v>14</v>
-      </c>
+      <c r="A297" s="6"/>
+      <c r="B297" s="7"/>
+      <c r="C297" s="7"/>
       <c r="D297" s="7"/>
-      <c t="s" r="E297" s="7">
-        <v>333</v>
-      </c>
-      <c r="F297" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G297" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H297" s="8">
-        <v>86</v>
-      </c>
-      <c t="s" r="I297" s="7">
-        <v>79</v>
-      </c>
-      <c t="s" r="J297" s="7">
-        <v>21</v>
-      </c>
+      <c r="E297" s="7"/>
+      <c r="F297" s="7"/>
+      <c r="G297" s="8"/>
+      <c r="H297" s="8"/>
+      <c r="I297" s="7"/>
+      <c r="J297" s="7"/>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c r="M297" s="7"/>
@@ -10448,29 +10462,29 @@
         <v>13</v>
       </c>
       <c r="B298" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c t="s" r="C298" s="7">
         <v>14</v>
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>190</v>
+        <v>83</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>183</v>
+        <v>21</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10481,29 +10495,29 @@
         <v>13</v>
       </c>
       <c r="B299" s="7">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c t="s" r="C299" s="7">
         <v>14</v>
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>34</v>
+        <v>90</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>334</v>
+        <v>186</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -10514,78 +10528,78 @@
         <v>13</v>
       </c>
       <c r="B300" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c t="s" r="C300" s="7">
         <v>14</v>
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>34</v>
+        <v>144</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>165</v>
+        <v>340</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c r="M300" s="7"/>
     </row>
     <row r="301" ht="14.25" customHeight="1">
-      <c r="A301" s="6"/>
-      <c r="B301" s="7"/>
-      <c r="C301" s="7"/>
+      <c t="s" r="A301" s="6">
+        <v>13</v>
+      </c>
+      <c r="B301" s="7">
+        <v>438</v>
+      </c>
+      <c t="s" r="C301" s="7">
+        <v>14</v>
+      </c>
       <c r="D301" s="7"/>
-      <c r="E301" s="7"/>
-      <c r="F301" s="7"/>
-      <c r="G301" s="8"/>
-      <c r="H301" s="8"/>
-      <c r="I301" s="7"/>
-      <c r="J301" s="7"/>
+      <c t="s" r="E301" s="7">
+        <v>339</v>
+      </c>
+      <c r="F301" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G301" s="8">
+        <v>144</v>
+      </c>
+      <c t="s" r="H301" s="8">
+        <v>34</v>
+      </c>
+      <c t="s" r="I301" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J301" s="7">
+        <v>168</v>
+      </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c r="M301" s="7"/>
     </row>
     <row r="302" ht="14.25" customHeight="1">
-      <c t="s" r="A302" s="6">
-        <v>13</v>
-      </c>
-      <c r="B302" s="7">
-        <v>825</v>
-      </c>
-      <c t="s" r="C302" s="7">
-        <v>14</v>
-      </c>
+      <c r="A302" s="6"/>
+      <c r="B302" s="7"/>
+      <c r="C302" s="7"/>
       <c r="D302" s="7"/>
-      <c t="s" r="E302" s="7">
-        <v>335</v>
-      </c>
-      <c r="F302" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G302" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="H302" s="8">
-        <v>336</v>
-      </c>
-      <c t="s" r="I302" s="7">
-        <v>108</v>
-      </c>
-      <c t="s" r="J302" s="7">
-        <v>337</v>
-      </c>
+      <c r="E302" s="7"/>
+      <c r="F302" s="7"/>
+      <c r="G302" s="8"/>
+      <c r="H302" s="8"/>
+      <c r="I302" s="7"/>
+      <c r="J302" s="7"/>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c r="M302" s="7"/>
@@ -10595,29 +10609,29 @@
         <v>13</v>
       </c>
       <c r="B303" s="7">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c t="s" r="C303" s="7">
         <v>14</v>
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>336</v>
+        <v>54</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>54</v>
+        <v>342</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>183</v>
+        <v>343</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10628,29 +10642,29 @@
         <v>13</v>
       </c>
       <c r="B304" s="7">
-        <v>876</v>
+        <v>826</v>
       </c>
       <c t="s" r="C304" s="7">
         <v>14</v>
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>54</v>
+        <v>342</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>338</v>
+        <v>54</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>223</v>
+        <v>186</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10661,29 +10675,29 @@
         <v>13</v>
       </c>
       <c r="B305" s="7">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c t="s" r="C305" s="7">
         <v>14</v>
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>338</v>
+        <v>54</v>
       </c>
       <c t="s" r="H305" s="8">
-        <v>54</v>
+        <v>344</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10694,29 +10708,29 @@
         <v>13</v>
       </c>
       <c r="B306" s="7">
-        <v>858</v>
+        <v>877</v>
       </c>
       <c t="s" r="C306" s="7">
         <v>14</v>
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F306" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G306" s="8">
-        <v>54</v>
+        <v>344</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>339</v>
+        <v>54</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>340</v>
+        <v>41</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>296</v>
+        <v>264</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -10724,81 +10738,81 @@
     </row>
     <row r="307" ht="14.25" customHeight="1">
       <c t="s" r="A307" s="6">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="B307" s="7">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c t="s" r="C307" s="7">
         <v>14</v>
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>339</v>
+        <v>54</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>54</v>
+        <v>345</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>342</v>
+        <v>298</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c r="M307" s="7"/>
     </row>
     <row r="308" ht="14.25" customHeight="1">
-      <c r="A308" s="6"/>
-      <c r="B308" s="7"/>
-      <c r="C308" s="7"/>
+      <c t="s" r="A308" s="6">
+        <v>42</v>
+      </c>
+      <c r="B308" s="7">
+        <v>859</v>
+      </c>
+      <c t="s" r="C308" s="7">
+        <v>14</v>
+      </c>
       <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
-      <c r="F308" s="7"/>
-      <c r="G308" s="8"/>
-      <c r="H308" s="8"/>
-      <c r="I308" s="7"/>
-      <c r="J308" s="7"/>
+      <c t="s" r="E308" s="7">
+        <v>341</v>
+      </c>
+      <c r="F308" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G308" s="8">
+        <v>345</v>
+      </c>
+      <c t="s" r="H308" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I308" s="7">
+        <v>347</v>
+      </c>
+      <c t="s" r="J308" s="7">
+        <v>348</v>
+      </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c r="M308" s="7"/>
     </row>
     <row r="309" ht="14.25" customHeight="1">
-      <c t="s" r="A309" s="6">
-        <v>13</v>
-      </c>
-      <c r="B309" s="7">
-        <v>125</v>
-      </c>
-      <c t="s" r="C309" s="7">
-        <v>14</v>
-      </c>
+      <c r="A309" s="6"/>
+      <c r="B309" s="7"/>
+      <c r="C309" s="7"/>
       <c r="D309" s="7"/>
-      <c t="s" r="E309" s="7">
-        <v>343</v>
-      </c>
-      <c r="F309" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G309" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H309" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="I309" s="7">
-        <v>344</v>
-      </c>
-      <c t="s" r="J309" s="7">
-        <v>256</v>
-      </c>
+      <c r="E309" s="7"/>
+      <c r="F309" s="7"/>
+      <c r="G309" s="8"/>
+      <c r="H309" s="8"/>
+      <c r="I309" s="7"/>
+      <c r="J309" s="7"/>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c r="M309" s="7"/>
@@ -10808,29 +10822,29 @@
         <v>13</v>
       </c>
       <c r="B310" s="7">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c t="s" r="C310" s="7">
         <v>14</v>
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>194</v>
+        <v>350</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>345</v>
+        <v>259</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10841,29 +10855,29 @@
         <v>13</v>
       </c>
       <c r="B311" s="7">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c t="s" r="C311" s="7">
         <v>14</v>
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>36</v>
+        <v>197</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>55</v>
+        <v>351</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -10874,29 +10888,29 @@
         <v>13</v>
       </c>
       <c r="B312" s="7">
-        <v>280</v>
+        <v>137</v>
       </c>
       <c t="s" r="C312" s="7">
         <v>14</v>
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>222</v>
+        <v>36</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>334</v>
+        <v>55</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -10907,78 +10921,78 @@
         <v>13</v>
       </c>
       <c r="B313" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c t="s" r="C313" s="7">
         <v>14</v>
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>109</v>
+        <v>54</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>54</v>
+        <v>113</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>102</v>
+        <v>225</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>89</v>
+        <v>340</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c r="M313" s="7"/>
     </row>
     <row r="314" ht="14.25" customHeight="1">
-      <c r="A314" s="6"/>
-      <c r="B314" s="7"/>
-      <c r="C314" s="7"/>
+      <c t="s" r="A314" s="6">
+        <v>13</v>
+      </c>
+      <c r="B314" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="C314" s="7">
+        <v>14</v>
+      </c>
       <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7"/>
-      <c r="G314" s="8"/>
-      <c r="H314" s="8"/>
-      <c r="I314" s="7"/>
-      <c r="J314" s="7"/>
+      <c t="s" r="E314" s="7">
+        <v>349</v>
+      </c>
+      <c r="F314" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G314" s="8">
+        <v>113</v>
+      </c>
+      <c t="s" r="H314" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I314" s="7">
+        <v>106</v>
+      </c>
+      <c t="s" r="J314" s="7">
+        <v>93</v>
+      </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c r="M314" s="7"/>
     </row>
     <row r="315" ht="15" customHeight="1">
-      <c t="s" r="A315" s="6">
-        <v>13</v>
-      </c>
-      <c r="B315" s="7">
-        <v>813</v>
-      </c>
-      <c t="s" r="C315" s="7">
-        <v>14</v>
-      </c>
+      <c r="A315" s="6"/>
+      <c r="B315" s="7"/>
+      <c r="C315" s="7"/>
       <c r="D315" s="7"/>
-      <c t="s" r="E315" s="7">
-        <v>346</v>
-      </c>
-      <c r="F315" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G315" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="H315" s="8">
-        <v>268</v>
-      </c>
-      <c t="s" r="I315" s="7">
-        <v>126</v>
-      </c>
-      <c t="s" r="J315" s="7">
-        <v>347</v>
-      </c>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
+      <c r="G315" s="8"/>
+      <c r="H315" s="8"/>
+      <c r="I315" s="7"/>
+      <c r="J315" s="7"/>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c r="M315" s="7"/>
@@ -10988,29 +11002,29 @@
         <v>13</v>
       </c>
       <c r="B316" s="7">
-        <v>970</v>
+        <v>813</v>
       </c>
       <c t="s" r="C316" s="7">
         <v>14</v>
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>268</v>
+        <v>54</v>
       </c>
       <c t="s" r="H316" s="8">
-        <v>17</v>
+        <v>271</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>257</v>
+        <v>129</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>226</v>
+        <v>353</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11021,29 +11035,29 @@
         <v>13</v>
       </c>
       <c r="B317" s="7">
-        <v>715</v>
+        <v>970</v>
       </c>
       <c t="s" r="C317" s="7">
         <v>14</v>
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F317" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G317" s="8">
+        <v>271</v>
+      </c>
+      <c t="s" r="H317" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H317" s="8">
-        <v>96</v>
-      </c>
       <c t="s" r="I317" s="7">
-        <v>145</v>
+        <v>260</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11054,78 +11068,78 @@
         <v>13</v>
       </c>
       <c r="B318" s="7">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c t="s" r="C318" s="7">
         <v>14</v>
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="F318" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>50</v>
+        <v>148</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>25</v>
+        <v>242</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c r="M318" s="7"/>
     </row>
     <row r="319" ht="14.25" customHeight="1">
-      <c r="A319" s="6"/>
-      <c r="B319" s="7"/>
-      <c r="C319" s="7"/>
+      <c t="s" r="A319" s="6">
+        <v>13</v>
+      </c>
+      <c r="B319" s="7">
+        <v>714</v>
+      </c>
+      <c t="s" r="C319" s="7">
+        <v>14</v>
+      </c>
       <c r="D319" s="7"/>
-      <c r="E319" s="7"/>
-      <c r="F319" s="7"/>
-      <c r="G319" s="8"/>
-      <c r="H319" s="8"/>
-      <c r="I319" s="7"/>
-      <c r="J319" s="7"/>
+      <c t="s" r="E319" s="7">
+        <v>352</v>
+      </c>
+      <c r="F319" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G319" s="8">
+        <v>100</v>
+      </c>
+      <c t="s" r="H319" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I319" s="7">
+        <v>50</v>
+      </c>
+      <c t="s" r="J319" s="7">
+        <v>25</v>
+      </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c r="M319" s="7"/>
     </row>
     <row r="320" ht="15" customHeight="1">
-      <c t="s" r="A320" s="6">
-        <v>13</v>
-      </c>
-      <c r="B320" s="7">
-        <v>337</v>
-      </c>
-      <c t="s" r="C320" s="7">
-        <v>14</v>
-      </c>
+      <c r="A320" s="6"/>
+      <c r="B320" s="7"/>
+      <c r="C320" s="7"/>
       <c r="D320" s="7"/>
-      <c t="s" r="E320" s="7">
-        <v>348</v>
-      </c>
-      <c r="F320" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G320" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="H320" s="8">
-        <v>96</v>
-      </c>
-      <c t="s" r="I320" s="7">
-        <v>256</v>
-      </c>
-      <c t="s" r="J320" s="7">
-        <v>19</v>
-      </c>
+      <c r="E320" s="7"/>
+      <c r="F320" s="7"/>
+      <c r="G320" s="8"/>
+      <c r="H320" s="8"/>
+      <c r="I320" s="7"/>
+      <c r="J320" s="7"/>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c r="M320" s="7"/>
@@ -11135,29 +11149,29 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>96</v>
+        <v>54</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>170</v>
+        <v>259</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>197</v>
+        <v>19</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11168,29 +11182,29 @@
         <v>13</v>
       </c>
       <c r="B322" s="7">
-        <v>214</v>
+        <v>324</v>
       </c>
       <c t="s" r="C322" s="7">
         <v>14</v>
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>54</v>
+        <v>100</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>202</v>
+        <v>54</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>122</v>
+        <v>173</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11201,78 +11215,78 @@
         <v>13</v>
       </c>
       <c r="B323" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="C323" s="7">
         <v>14</v>
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>202</v>
+        <v>54</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>54</v>
+        <v>205</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>172</v>
+        <v>23</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c r="M323" s="7"/>
     </row>
     <row r="324" ht="14.25" customHeight="1">
-      <c r="A324" s="6"/>
-      <c r="B324" s="7"/>
-      <c r="C324" s="7"/>
+      <c t="s" r="A324" s="6">
+        <v>13</v>
+      </c>
+      <c r="B324" s="7">
+        <v>213</v>
+      </c>
+      <c t="s" r="C324" s="7">
+        <v>14</v>
+      </c>
       <c r="D324" s="7"/>
-      <c r="E324" s="7"/>
-      <c r="F324" s="7"/>
-      <c r="G324" s="8"/>
-      <c r="H324" s="8"/>
-      <c r="I324" s="7"/>
-      <c r="J324" s="7"/>
+      <c t="s" r="E324" s="7">
+        <v>354</v>
+      </c>
+      <c r="F324" s="7">
+        <v>320</v>
+      </c>
+      <c t="s" r="G324" s="8">
+        <v>205</v>
+      </c>
+      <c t="s" r="H324" s="8">
+        <v>54</v>
+      </c>
+      <c t="s" r="I324" s="7">
+        <v>149</v>
+      </c>
+      <c t="s" r="J324" s="7">
+        <v>175</v>
+      </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c r="M324" s="7"/>
     </row>
     <row r="325" ht="15" customHeight="1">
-      <c t="s" r="A325" s="6">
-        <v>13</v>
-      </c>
-      <c r="B325" s="7">
-        <v>122</v>
-      </c>
-      <c t="s" r="C325" s="7">
-        <v>14</v>
-      </c>
+      <c r="A325" s="6"/>
+      <c r="B325" s="7"/>
+      <c r="C325" s="7"/>
       <c r="D325" s="7"/>
-      <c t="s" r="E325" s="7">
-        <v>349</v>
-      </c>
-      <c r="F325" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G325" s="8">
-        <v>54</v>
-      </c>
-      <c t="s" r="H325" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I325" s="7">
-        <v>350</v>
-      </c>
-      <c t="s" r="J325" s="7">
-        <v>351</v>
-      </c>
+      <c r="E325" s="7"/>
+      <c r="F325" s="7"/>
+      <c r="G325" s="8"/>
+      <c r="H325" s="8"/>
+      <c r="I325" s="7"/>
+      <c r="J325" s="7"/>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c r="M325" s="7"/>
@@ -11282,29 +11296,29 @@
         <v>13</v>
       </c>
       <c r="B326" s="7">
-        <v>463</v>
+        <v>382</v>
       </c>
       <c t="s" r="C326" s="7">
         <v>14</v>
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>182</v>
+        <v>356</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>99</v>
+        <v>291</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11315,29 +11329,29 @@
         <v>13</v>
       </c>
       <c r="B327" s="7">
-        <v>464</v>
+        <v>383</v>
       </c>
       <c t="s" r="C327" s="7">
         <v>14</v>
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>121</v>
+        <v>326</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>112</v>
+        <v>272</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11348,29 +11362,29 @@
         <v>13</v>
       </c>
       <c r="B328" s="7">
-        <v>567</v>
+        <v>374</v>
       </c>
       <c t="s" r="C328" s="7">
         <v>14</v>
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="H328" s="8">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>239</v>
+        <v>277</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11381,29 +11395,29 @@
         <v>13</v>
       </c>
       <c r="B329" s="7">
-        <v>568</v>
+        <v>375</v>
       </c>
       <c t="s" r="C329" s="7">
         <v>14</v>
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F329" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G329" s="8">
-        <v>196</v>
+        <v>320</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>235</v>
+        <v>269</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11414,29 +11428,29 @@
         <v>13</v>
       </c>
       <c r="B330" s="7">
-        <v>7238</v>
+        <v>3948</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>14</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F330" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>353</v>
+        <v>170</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
@@ -11447,29 +11461,29 @@
         <v>42</v>
       </c>
       <c r="B331" s="7">
-        <v>7239</v>
+        <v>3949</v>
       </c>
       <c t="s" r="C331" s="7">
         <v>14</v>
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>354</v>
+        <v>232</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>355</v>
+        <v>281</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11502,7 +11516,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11511,10 +11525,10 @@
         <v>34</v>
       </c>
       <c t="s" r="H333" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>38</v>
@@ -11535,13 +11549,13 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G334" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H334" s="8">
         <v>34</v>
@@ -11550,7 +11564,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -11568,7 +11582,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -11580,10 +11594,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11601,7 +11615,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F336" s="7">
         <v>321</v>
@@ -11613,10 +11627,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>350</v>
+        <v>332</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11649,7 +11663,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -11661,10 +11675,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -11682,7 +11696,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11694,10 +11708,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11715,7 +11729,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -11724,13 +11738,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>35</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11748,19 +11762,19 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J341" s="7">
         <v>36</v>
@@ -11781,7 +11795,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -11790,13 +11804,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H342" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -11814,22 +11828,22 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G343" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="H343" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11847,7 +11861,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11856,13 +11870,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -11880,22 +11894,22 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -11928,7 +11942,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -11937,13 +11951,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -11961,22 +11975,22 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -11994,7 +12008,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12003,13 +12017,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12027,22 +12041,22 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12060,7 +12074,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12075,7 +12089,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
@@ -12093,7 +12107,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12105,10 +12119,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12141,7 +12155,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12153,10 +12167,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12174,7 +12188,7 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
@@ -12183,13 +12197,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H355" s="8">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12207,22 +12221,22 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G356" s="8">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="H356" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
@@ -12240,7 +12254,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12249,13 +12263,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12273,22 +12287,22 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>352</v>
+        <v>334</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12321,7 +12335,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -12330,13 +12344,13 @@
         <v>29</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12354,22 +12368,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12387,22 +12401,22 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G362" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12420,22 +12434,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="H363" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12453,22 +12467,22 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G364" s="8">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12501,13 +12515,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>54</v>
@@ -12516,7 +12530,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12549,7 +12563,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12558,10 +12572,10 @@
         <v>54</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>38</v>
@@ -12582,13 +12596,13 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>54</v>
@@ -12597,7 +12611,7 @@
         <v>55</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12615,7 +12629,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12627,10 +12641,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12648,7 +12662,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -12660,10 +12674,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -12696,7 +12710,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -12705,13 +12719,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>45</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12729,22 +12743,22 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -12762,7 +12776,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -12771,13 +12785,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12795,22 +12809,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12828,7 +12842,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -12840,7 +12854,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c t="s" r="J377" s="7">
         <v>41</v>
@@ -12861,7 +12875,7 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F378" s="7">
         <v>321</v>
@@ -12873,10 +12887,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I378" s="7">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -12909,7 +12923,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -12918,13 +12932,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H380" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="I380" s="7">
         <v>60</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -12942,13 +12956,13 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G381" s="8">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c t="s" r="H381" s="8">
         <v>54</v>
@@ -12957,7 +12971,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -12975,7 +12989,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -12987,10 +13001,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13008,7 +13022,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13020,7 +13034,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>23</v>
@@ -13041,7 +13055,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13050,13 +13064,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13074,13 +13088,13 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>54</v>
@@ -13089,7 +13103,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13122,7 +13136,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13131,13 +13145,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13155,13 +13169,13 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>54</v>
@@ -13170,7 +13184,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13188,7 +13202,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13200,10 +13214,10 @@
         <v>33</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13236,7 +13250,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13248,10 +13262,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13269,7 +13283,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13302,7 +13316,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13335,7 +13349,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13347,10 +13361,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13368,7 +13382,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13377,13 +13391,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13401,19 +13415,19 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J396" s="7">
         <v>31</v>
@@ -13449,7 +13463,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13461,10 +13475,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13482,7 +13496,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
@@ -13491,7 +13505,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H399" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="I399" s="7">
         <v>65</v>
@@ -13515,22 +13529,22 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F400" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G400" s="8">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c t="s" r="H400" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c t="s" r="J400" s="7">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K400" s="7"/>
       <c r="L400" s="7"/>
@@ -13559,23 +13573,23 @@
         <v>5805</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>49</v>
@@ -13592,26 +13606,26 @@
         <v>5806</v>
       </c>
       <c t="s" r="C403" s="7">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F403" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G403" s="8">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I403" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13644,22 +13658,22 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13677,22 +13691,22 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G406" s="8">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c t="s" r="H406" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I406" s="7">
         <v>22</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -13725,22 +13739,22 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G408" s="8">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c t="s" r="H408" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13758,7 +13772,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -13770,7 +13784,7 @@
         <v>34</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c t="s" r="J409" s="7">
         <v>41</v>
@@ -13791,7 +13805,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
@@ -13803,10 +13817,10 @@
         <v>54</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13839,13 +13853,13 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>54</v>
@@ -13854,7 +13868,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -13872,7 +13886,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -13881,13 +13895,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H413" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -13905,22 +13919,22 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G414" s="8">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c t="s" r="H414" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>286</v>
+        <v>72</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -13953,22 +13967,22 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>34</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -13986,7 +14000,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -13998,7 +14012,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>38</v>
@@ -14019,7 +14033,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14028,13 +14042,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14052,22 +14066,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="H419" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14085,22 +14099,22 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G420" s="8">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14133,7 +14147,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14142,13 +14156,13 @@
         <v>54</v>
       </c>
       <c t="s" r="H422" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14166,22 +14180,22 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G423" s="8">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c t="s" r="H423" s="8">
         <v>54</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14189,7 +14203,7 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c t="s" r="A424" s="9">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -14209,7 +14223,7 @@
     <row r="425" ht="66" customHeight="1"/>
     <row r="426" ht="16.5" customHeight="1">
       <c t="s" r="A426" s="10">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B426" s="10"/>
       <c r="C426" s="10"/>
@@ -14222,7 +14236,7 @@
       <c r="J426" s="10"/>
       <c r="K426" s="10"/>
       <c t="s" r="L426" s="11">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="M426" s="11"/>
       <c r="N426" s="11"/>

--- a/Data/FlightPlan/FPL_16OCT26.xlsx
+++ b/Data/FlightPlan/FPL_16OCT26.xlsx
@@ -236,6 +236,9 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>14:15</t>
+  </si>
+  <si>
     <t>CZX</t>
   </si>
   <si>
@@ -323,624 +326,639 @@
     <t>11:00</t>
   </si>
   <si>
+    <t>11:14</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>NOZ</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>00:15</t>
+  </si>
+  <si>
+    <t>06:15</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>09:30</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>09:33</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>CGK</t>
+  </si>
+  <si>
+    <t>08:40</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>00:40</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>09:01</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>15:40</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>06:47</t>
+  </si>
+  <si>
+    <t>08:18</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A534</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>10:14</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>DLI</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>01:35</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>14:29</t>
+  </si>
+  <si>
+    <t>17:25</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>11:19</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>10:20</t>
+  </si>
+  <si>
+    <t>10:26</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>16:10</t>
+  </si>
+  <si>
+    <t>16:40</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>VN-A544</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>21:05</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
     <t>11:06</t>
   </si>
   <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>NOZ</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>00:15</t>
-  </si>
-  <si>
-    <t>06:15</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>09:30</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>09:33</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>CGK</t>
-  </si>
-  <si>
-    <t>08:40</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>00:40</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>09:01</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>06:47</t>
-  </si>
-  <si>
-    <t>08:18</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>VN-A534</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>10:14</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>DLI</t>
-  </si>
-  <si>
-    <t>15:40</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>01:35</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>17:25</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>11:19</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>10:20</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>16:10</t>
-  </si>
-  <si>
-    <t>16:40</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>VN-A544</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>21:05</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
     <t>VN-A640</t>
   </si>
   <si>
@@ -962,6 +980,9 @@
     <t>07:05</t>
   </si>
   <si>
+    <t>11:17</t>
+  </si>
+  <si>
     <t>SAI</t>
   </si>
   <si>
@@ -1025,6 +1046,9 @@
     <t>11:05</t>
   </si>
   <si>
+    <t>14:18</t>
+  </si>
+  <si>
     <t>KHH</t>
   </si>
   <si>
@@ -1064,9 +1088,6 @@
     <t>10:05</t>
   </si>
   <si>
-    <t>10:26</t>
-  </si>
-  <si>
     <t>VN-A653</t>
   </si>
   <si>
@@ -1103,6 +1124,9 @@
     <t>VN-A657</t>
   </si>
   <si>
+    <t>11:33</t>
+  </si>
+  <si>
     <t>VN-A658</t>
   </si>
   <si>
@@ -1118,6 +1142,9 @@
     <t>12:35</t>
   </si>
   <si>
+    <t>12:53</t>
+  </si>
+  <si>
     <t>MNL</t>
   </si>
   <si>
@@ -1139,6 +1166,9 @@
     <t>11:50</t>
   </si>
   <si>
+    <t>11:46</t>
+  </si>
+  <si>
     <t>VN-A667</t>
   </si>
   <si>
@@ -1151,6 +1181,9 @@
     <t>VN-A668</t>
   </si>
   <si>
+    <t>10:37</t>
+  </si>
+  <si>
     <t>VN-A669</t>
   </si>
   <si>
@@ -1241,6 +1274,9 @@
     <t>VN-A693</t>
   </si>
   <si>
+    <t>12:39</t>
+  </si>
+  <si>
     <t>VN-A697</t>
   </si>
   <si>
@@ -1259,7 +1295,7 @@
     <t>KZN</t>
   </si>
   <si>
-    <t>15:16</t>
+    <t>15:27</t>
   </si>
   <si>
     <t>VN-A811</t>
@@ -1280,6 +1316,9 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>16:42</t>
+  </si>
+  <si>
     <t>VN-A814</t>
   </si>
   <si>
@@ -1310,7 +1349,7 @@
     <t>Total Record(s): 342</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 16, 2026 09:09</t>
+    <t xml:space="preserve">Generated on  Oct 16, 2026 10:08</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2569,7 +2608,9 @@
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
-      <c r="M30" s="7"/>
+      <c t="s" r="M30" s="7">
+        <v>75</v>
+      </c>
     </row>
     <row r="31" ht="14.25" customHeight="1">
       <c t="s" r="A31" s="6">
@@ -2592,20 +2633,20 @@
         <v>72</v>
       </c>
       <c t="s" r="H31" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="I31" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="K31" s="7">
         <v>23</v>
       </c>
       <c r="L31" s="7"/>
       <c t="s" r="M31" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -2626,19 +2667,19 @@
         <v>321</v>
       </c>
       <c t="s" r="G32" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H32" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="K32" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L32" s="7"/>
       <c t="s" r="M32" s="7">
@@ -2672,7 +2713,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2681,13 +2722,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H34" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="I34" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J34" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
@@ -2705,22 +2746,22 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2738,7 +2779,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2750,10 +2791,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2786,7 +2827,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2795,13 +2836,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H38" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2819,22 +2860,22 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G39" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H39" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2852,7 +2893,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -2864,10 +2905,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I40" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J40" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -2885,7 +2926,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2894,10 +2935,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="J41" s="7">
         <v>70</v>
@@ -2929,11 +2970,11 @@
         <v>2869</v>
       </c>
       <c t="s" r="C43" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2942,18 +2983,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -2968,13 +3009,13 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>57</v>
@@ -3001,7 +3042,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3013,10 +3054,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3030,11 +3071,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C46" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3043,20 +3084,20 @@
         <v>35</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c t="s" r="K46" s="7">
         <v>42</v>
       </c>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3067,33 +3108,33 @@
         <v>5069</v>
       </c>
       <c t="s" r="C47" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I47" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c t="s" r="J47" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="K47" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3104,11 +3145,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C48" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3117,16 +3158,16 @@
         <v>35</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c t="s" r="I48" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c t="s" r="K48" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
@@ -3160,7 +3201,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3169,13 +3210,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3195,27 +3236,27 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
+        <v>118</v>
+      </c>
+      <c r="F51" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G51" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="H51" s="8">
+        <v>57</v>
+      </c>
+      <c t="s" r="I51" s="7">
+        <v>121</v>
+      </c>
+      <c t="s" r="J51" s="7">
         <v>117</v>
-      </c>
-      <c r="F51" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G51" s="8">
-        <v>118</v>
-      </c>
-      <c t="s" r="H51" s="8">
-        <v>57</v>
-      </c>
-      <c t="s" r="I51" s="7">
-        <v>120</v>
-      </c>
-      <c t="s" r="J51" s="7">
-        <v>116</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3230,7 +3271,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3239,13 +3280,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3263,13 +3304,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>57</v>
@@ -3296,7 +3337,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3308,7 +3349,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J54" s="7">
         <v>53</v>
@@ -3329,7 +3370,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3341,10 +3382,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c t="s" r="J55" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3362,7 +3403,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3374,10 +3415,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3395,7 +3436,7 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
@@ -3407,10 +3448,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
@@ -3443,7 +3484,7 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
@@ -3452,18 +3493,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
       <c t="s" r="M59" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="60" ht="15" customHeight="1">
@@ -3478,19 +3519,19 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H60" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J60" s="7">
         <v>26</v>
@@ -3511,7 +3552,7 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F61" s="7">
         <v>321</v>
@@ -3520,13 +3561,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H61" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="I61" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
@@ -3544,22 +3585,22 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G62" s="8">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="H62" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
@@ -3592,7 +3633,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3601,18 +3642,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H64" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3627,40 +3668,42 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>147</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c t="s" r="A66" s="6">
         <v>13</v>
       </c>
       <c r="B66" s="7">
-        <v>515</v>
+        <v>453</v>
       </c>
       <c t="s" r="C66" s="7">
         <v>14</v>
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3669,13 +3712,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H66" s="8">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c t="s" r="I66" s="7">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3686,29 +3729,29 @@
         <v>13</v>
       </c>
       <c r="B67" s="7">
-        <v>508</v>
+        <v>456</v>
       </c>
       <c t="s" r="C67" s="7">
         <v>14</v>
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G67" s="8">
-        <v>17</v>
+        <v>102</v>
       </c>
       <c t="s" r="H67" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c t="s" r="J67" s="7">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
@@ -3719,14 +3762,14 @@
         <v>13</v>
       </c>
       <c r="B68" s="7">
-        <v>773</v>
+        <v>521</v>
       </c>
       <c t="s" r="C68" s="7">
         <v>14</v>
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3735,13 +3778,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>150</v>
+        <v>54</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
@@ -3752,29 +3795,29 @@
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>776</v>
+        <v>518</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
@@ -3792,7 +3835,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -3804,10 +3847,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3840,7 +3883,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -3849,18 +3892,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H72" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -3875,27 +3918,27 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="H73" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
       <c t="s" r="M73" s="7">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" ht="14.25" customHeight="1">
@@ -3910,7 +3953,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -3919,18 +3962,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c t="s" r="M74" s="7">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
@@ -3945,19 +3988,19 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G75" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H75" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J75" s="7">
         <v>40</v>
@@ -3978,7 +4021,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -3990,10 +4033,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I76" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J76" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
@@ -4011,7 +4054,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4020,13 +4063,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I77" s="7">
         <v>54</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
@@ -4044,22 +4087,22 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H78" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4092,7 +4135,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4101,18 +4144,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4127,13 +4170,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>57</v>
@@ -4142,12 +4185,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4162,7 +4205,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4174,10 +4217,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I82" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J82" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -4195,7 +4238,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4207,10 +4250,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4228,7 +4271,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4237,13 +4280,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4261,13 +4304,13 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>35</v>
@@ -4294,7 +4337,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4351,7 +4394,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H88" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="I88" s="7">
         <v>178</v>
@@ -4385,13 +4428,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G89" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="H89" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>181</v>
@@ -4457,7 +4500,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>185</v>
@@ -4502,7 +4545,7 @@
         <v>35</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>178</v>
@@ -4512,7 +4555,9 @@
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
+      <c t="s" r="M93" s="7">
+        <v>73</v>
+      </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
       <c t="s" r="A94" s="6">
@@ -4532,7 +4577,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>35</v>
@@ -4568,10 +4613,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>24</v>
@@ -4598,13 +4643,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H96" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>189</v>
@@ -4668,7 +4713,7 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>453</v>
+        <v>515</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
@@ -4684,13 +4729,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>133</v>
+        <v>194</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>194</v>
+        <v>40</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -4701,7 +4746,7 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>456</v>
+        <v>508</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
@@ -4714,16 +4759,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c t="s" r="H100" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4734,7 +4779,7 @@
         <v>13</v>
       </c>
       <c r="B101" s="7">
-        <v>521</v>
+        <v>773</v>
       </c>
       <c t="s" r="C101" s="7">
         <v>14</v>
@@ -4750,13 +4795,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H101" s="8">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c t="s" r="I101" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c t="s" r="J101" s="7">
-        <v>54</v>
+        <v>198</v>
       </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -4767,7 +4812,7 @@
         <v>13</v>
       </c>
       <c r="B102" s="7">
-        <v>518</v>
+        <v>776</v>
       </c>
       <c t="s" r="C102" s="7">
         <v>14</v>
@@ -4780,16 +4825,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G102" s="8">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c t="s" r="H102" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -4855,7 +4900,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4867,14 +4912,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
+      <c t="s" r="M105" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c t="s" r="A106" s="6">
@@ -4888,7 +4935,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -4921,7 +4968,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4933,10 +4980,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4954,7 +5001,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -4969,7 +5016,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4987,7 +5034,7 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4996,13 +5043,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
@@ -5020,22 +5067,22 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
+        <v>201</v>
+      </c>
+      <c r="F110" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G110" s="8">
+        <v>119</v>
+      </c>
+      <c t="s" r="H110" s="8">
+        <v>57</v>
+      </c>
+      <c t="s" r="I110" s="7">
         <v>199</v>
       </c>
-      <c r="F110" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G110" s="8">
-        <v>118</v>
-      </c>
-      <c t="s" r="H110" s="8">
-        <v>57</v>
-      </c>
-      <c t="s" r="I110" s="7">
-        <v>151</v>
-      </c>
       <c t="s" r="J110" s="7">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5068,7 +5115,7 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5077,10 +5124,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J112" s="7">
         <v>22</v>
@@ -5101,19 +5148,19 @@
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>58</v>
@@ -5134,7 +5181,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5146,10 +5193,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5167,7 +5214,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5179,10 +5226,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -5215,7 +5262,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5224,13 +5271,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5248,22 +5295,22 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="H118" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5281,7 +5328,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5290,13 +5337,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5314,22 +5361,22 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5347,7 +5394,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5356,13 +5403,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5380,19 +5427,19 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>61</v>
@@ -5428,7 +5475,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5440,15 +5487,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J124" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5463,7 +5510,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5475,7 +5522,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c t="s" r="J125" s="7">
         <v>51</v>
@@ -5511,7 +5558,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5523,14 +5570,16 @@
         <v>57</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
-      <c r="M127" s="7"/>
+      <c t="s" r="M127" s="7">
+        <v>196</v>
+      </c>
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c t="s" r="A128" s="6">
@@ -5544,7 +5593,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5553,20 +5602,20 @@
         <v>57</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="K128" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L128" s="7"/>
       <c t="s" r="M128" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="129" ht="14.25" customHeight="1">
@@ -5581,22 +5630,22 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>30</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5629,7 +5678,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5641,10 +5690,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5660,11 +5709,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C132" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5676,10 +5725,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5697,7 +5746,7 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
@@ -5709,7 +5758,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c t="s" r="J133" s="7">
         <v>69</v>
@@ -5745,7 +5794,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5754,13 +5803,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H135" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5778,22 +5827,22 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G136" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H136" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5811,7 +5860,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5823,10 +5872,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5844,7 +5893,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5856,10 +5905,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -5877,7 +5926,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -5889,10 +5938,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -5921,31 +5970,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G141" s="8">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c t="s" r="H141" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -5956,11 +6005,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5972,10 +6021,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5989,11 +6038,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C143" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6005,17 +6054,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c t="s" r="J143" s="7">
         <v>55</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6045,7 +6094,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6057,15 +6106,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6080,7 +6129,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6092,13 +6141,13 @@
         <v>57</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
@@ -6117,7 +6166,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6129,17 +6178,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="K147" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6154,7 +6203,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6169,14 +6218,14 @@
         <v>183</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6191,7 +6240,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6203,17 +6252,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c t="s" r="K149" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6243,7 +6292,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6255,15 +6304,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6278,7 +6327,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6290,10 +6339,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6311,7 +6360,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6323,10 +6372,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6344,7 +6393,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6359,7 +6408,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6392,26 +6441,28 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
-      <c r="M156" s="7"/>
+      <c t="s" r="M156" s="7">
+        <v>270</v>
+      </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c t="s" r="A157" s="6">
@@ -6425,7 +6476,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6434,13 +6485,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6473,7 +6524,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6485,10 +6536,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6508,7 +6559,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6517,10 +6568,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J160" s="7">
         <v>73</v>
@@ -6528,7 +6579,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -6543,22 +6594,22 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c t="s" r="H161" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6576,7 +6627,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6585,7 +6636,7 @@
         <v>57</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>23</v>
@@ -6609,22 +6660,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6657,7 +6708,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6669,14 +6720,16 @@
         <v>39</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
-      <c r="M165" s="7"/>
+      <c t="s" r="M165" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
       <c t="s" r="A166" s="6">
@@ -6690,7 +6743,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6702,10 +6755,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6723,7 +6776,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6738,7 +6791,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6756,7 +6809,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6768,10 +6821,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -6789,7 +6842,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6801,10 +6854,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -6837,7 +6890,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6846,18 +6899,18 @@
         <v>35</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -6872,26 +6925,28 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
-      <c r="M172" s="7"/>
+      <c t="s" r="M172" s="7">
+        <v>275</v>
+      </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
       <c t="s" r="A173" s="6">
@@ -6905,7 +6960,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -6914,17 +6969,21 @@
         <v>35</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>92</v>
-      </c>
-      <c r="K173" s="7"/>
+        <v>93</v>
+      </c>
+      <c t="s" r="K173" s="7">
+        <v>22</v>
+      </c>
       <c r="L173" s="7"/>
-      <c r="M173" s="7"/>
+      <c t="s" r="M173" s="7">
+        <v>230</v>
+      </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
       <c t="s" r="A174" s="6">
@@ -6938,26 +6997,30 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>254</v>
-      </c>
-      <c r="K174" s="7"/>
+        <v>256</v>
+      </c>
+      <c t="s" r="K174" s="7">
+        <v>212</v>
+      </c>
       <c r="L174" s="7"/>
-      <c r="M174" s="7"/>
+      <c t="s" r="M174" s="7">
+        <v>163</v>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1">
       <c t="s" r="A175" s="6">
@@ -6971,7 +7034,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6980,17 +7043,21 @@
         <v>35</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>256</v>
-      </c>
-      <c r="K175" s="7"/>
+        <v>258</v>
+      </c>
+      <c t="s" r="K175" s="7">
+        <v>150</v>
+      </c>
       <c r="L175" s="7"/>
-      <c r="M175" s="7"/>
+      <c t="s" r="M175" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
       <c t="s" r="A176" s="6">
@@ -7004,26 +7071,30 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>242</v>
-      </c>
-      <c r="K176" s="7"/>
+        <v>244</v>
+      </c>
+      <c t="s" r="K176" s="7">
+        <v>54</v>
+      </c>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>97</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="6"/>
@@ -7052,7 +7123,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7064,7 +7135,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J178" s="7">
         <v>187</v>
@@ -7072,7 +7143,7 @@
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7087,7 +7158,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7099,10 +7170,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7120,7 +7191,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7135,7 +7206,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -7168,7 +7239,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7188,7 +7259,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7203,7 +7274,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7212,18 +7283,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7238,22 +7309,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H184" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7271,7 +7342,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7283,10 +7354,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="J185" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -7304,7 +7375,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7316,17 +7387,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="K186" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7341,7 +7412,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7353,7 +7424,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>42</v>
@@ -7389,7 +7460,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7398,13 +7469,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H189" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7422,19 +7493,19 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G190" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="H190" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>148</v>
+        <v>196</v>
       </c>
       <c t="s" r="J190" s="7">
         <v>53</v>
@@ -7455,7 +7526,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7464,13 +7535,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7488,13 +7559,13 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="H192" s="8">
         <v>57</v>
@@ -7503,7 +7574,7 @@
         <v>183</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7521,7 +7592,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7533,10 +7604,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7554,7 +7625,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7566,10 +7637,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7602,7 +7673,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7611,18 +7682,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="I196" s="7">
         <v>50</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -7637,22 +7708,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -7670,7 +7741,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7679,13 +7750,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7703,22 +7774,22 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7751,7 +7822,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7760,18 +7831,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -7786,19 +7857,19 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c t="s" r="J202" s="7">
         <v>178</v>
@@ -7806,7 +7877,7 @@
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -7821,16 +7892,16 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I203" s="7">
         <v>179</v>
@@ -7840,7 +7911,9 @@
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
-      <c r="M203" s="7"/>
+      <c t="s" r="M203" s="7">
+        <v>307</v>
+      </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
       <c t="s" r="A204" s="6">
@@ -7854,22 +7927,22 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H204" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7887,7 +7960,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7896,13 +7969,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7920,19 +7993,19 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G206" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H206" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>189</v>
@@ -7953,7 +8026,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -7965,10 +8038,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7986,7 +8059,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7998,10 +8071,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -8034,7 +8107,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8046,15 +8119,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8069,7 +8142,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8089,7 +8162,7 @@
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>103</v>
+        <v>315</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8104,7 +8177,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8113,13 +8186,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>188</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8137,22 +8210,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H213" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8170,22 +8243,22 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G214" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H214" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8203,22 +8276,22 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H215" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8251,7 +8324,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8263,15 +8336,15 @@
         <v>72</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8286,7 +8359,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8298,10 +8371,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8319,7 +8392,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8328,13 +8401,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8352,13 +8425,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>57</v>
@@ -8367,7 +8440,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8400,7 +8473,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8412,15 +8485,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8435,7 +8508,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8447,17 +8520,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c t="s" r="K223" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8472,7 +8545,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8490,11 +8563,11 @@
         <v>192</v>
       </c>
       <c t="s" r="K224" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>103</v>
+        <v>323</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8509,7 +8582,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8521,17 +8594,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c t="s" r="J225" s="7">
         <v>38</v>
       </c>
       <c t="s" r="K225" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L225" s="7"/>
       <c t="s" r="M225" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="226" ht="14.25" customHeight="1">
@@ -8546,7 +8619,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8558,17 +8631,17 @@
         <v>35</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="K226" s="7">
         <v>74</v>
       </c>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -8583,7 +8656,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8592,13 +8665,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8616,19 +8689,19 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>27</v>
@@ -8649,7 +8722,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8658,13 +8731,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H229" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8682,22 +8755,22 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H230" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8730,7 +8803,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8739,18 +8812,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -8765,13 +8838,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>57</v>
@@ -8780,25 +8853,27 @@
         <v>36</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
-      <c r="M233" s="7"/>
+      <c t="s" r="M233" s="7">
+        <v>275</v>
+      </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
       <c t="s" r="A234" s="6">
         <v>13</v>
       </c>
       <c r="B234" s="7">
-        <v>138</v>
+        <v>214</v>
       </c>
       <c t="s" r="C234" s="7">
         <v>14</v>
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8807,13 +8882,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H234" s="8">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>252</v>
+        <v>136</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8824,29 +8899,29 @@
         <v>13</v>
       </c>
       <c r="B235" s="7">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>35</v>
+        <v>221</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>230</v>
+        <v>107</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>274</v>
+        <v>189</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -8879,19 +8954,19 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J237" s="7">
         <v>188</v>
@@ -8899,7 +8974,7 @@
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -8914,7 +8989,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8923,10 +8998,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>42</v>
@@ -8947,13 +9022,13 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c t="s" r="H239" s="8">
         <v>35</v>
@@ -8962,7 +9037,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -8980,7 +9055,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8992,10 +9067,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9028,7 +9103,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9037,13 +9112,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H242" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9061,13 +9136,13 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G243" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H243" s="8">
         <v>17</v>
@@ -9076,7 +9151,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9109,7 +9184,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9121,15 +9196,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c t="s" r="M245" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="246" ht="14.25" customHeight="1">
@@ -9144,7 +9219,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9153,13 +9228,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H246" s="8">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9177,13 +9252,13 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c t="s" r="H247" s="8">
         <v>57</v>
@@ -9192,7 +9267,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9210,7 +9285,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9222,7 +9297,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="J248" s="7">
         <v>50</v>
@@ -9258,7 +9333,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9270,10 +9345,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -9291,7 +9366,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9306,7 +9381,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9324,7 +9399,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9339,7 +9414,7 @@
         <v>43</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9357,7 +9432,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9369,10 +9444,10 @@
         <v>30</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9405,7 +9480,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9417,14 +9492,16 @@
         <v>35</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J255" s="7">
         <v>74</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>345</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c t="s" r="A256" s="6">
@@ -9438,7 +9515,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9447,13 +9524,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H256" s="8">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>150</v>
+        <v>198</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9471,22 +9548,22 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c t="s" r="H257" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9519,7 +9596,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9531,7 +9608,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>40</v>
@@ -9552,7 +9629,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9567,7 +9644,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9585,7 +9662,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9597,7 +9674,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>29</v>
@@ -9618,7 +9695,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9627,10 +9704,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c t="s" r="J262" s="7">
         <v>50</v>
@@ -9666,7 +9743,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -9675,18 +9752,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9701,27 +9778,27 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -9736,7 +9813,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -9745,13 +9822,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9769,22 +9846,22 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
@@ -9802,7 +9879,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -9811,13 +9888,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -9835,22 +9912,22 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9868,7 +9945,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -9880,10 +9957,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9916,7 +9993,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9925,18 +10002,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>351</v>
+        <v>203</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -9951,22 +10028,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9984,7 +10061,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9993,10 +10070,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J274" s="7">
         <v>51</v>
@@ -10017,22 +10094,22 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>149</v>
+        <v>197</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -10065,7 +10142,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10074,13 +10151,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c t="s" r="I277" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10098,22 +10175,22 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G278" s="8">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c t="s" r="H278" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10146,7 +10223,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
@@ -10158,15 +10235,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>359</v>
+        <v>366</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10181,7 +10258,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10190,10 +10267,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>38</v>
@@ -10214,22 +10291,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10247,7 +10324,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -10256,13 +10333,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10280,22 +10357,22 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10313,7 +10390,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10322,13 +10399,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10346,22 +10423,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10394,7 +10471,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10403,18 +10480,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
       <c t="s" r="M288" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="289" ht="14.25" customHeight="1">
@@ -10429,26 +10506,28 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
-      <c r="M289" s="7"/>
+      <c t="s" r="M289" s="7">
+        <v>371</v>
+      </c>
     </row>
     <row r="290" ht="15" customHeight="1">
       <c t="s" r="A290" s="6">
@@ -10462,7 +10541,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10471,13 +10550,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10495,22 +10574,22 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10528,7 +10607,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10537,13 +10616,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10561,22 +10640,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10609,7 +10688,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F295" s="7">
         <v>320</v>
@@ -10618,10 +10697,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H295" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J295" s="7">
         <v>22</v>
@@ -10642,22 +10721,22 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F296" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G296" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H296" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10675,7 +10754,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -10684,13 +10763,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10708,19 +10787,19 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>183</v>
@@ -10756,7 +10835,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10765,17 +10844,19 @@
         <v>57</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
-      <c r="M300" s="7"/>
+      <c t="s" r="M300" s="7">
+        <v>377</v>
+      </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
       <c t="s" r="A301" s="6">
@@ -10789,13 +10870,13 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>57</v>
@@ -10804,7 +10885,7 @@
         <v>74</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10822,7 +10903,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10831,13 +10912,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>151</v>
+        <v>199</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -10855,19 +10936,19 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>27</v>
@@ -10888,7 +10969,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10897,13 +10978,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10921,22 +11002,22 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10969,7 +11050,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -10981,15 +11062,15 @@
         <v>57</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11004,7 +11085,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11016,14 +11097,16 @@
         <v>35</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
-      <c r="M308" s="7"/>
+      <c t="s" r="M308" s="7">
+        <v>385</v>
+      </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
       <c t="s" r="A309" s="6">
@@ -11037,7 +11120,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11070,7 +11153,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11079,13 +11162,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H310" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11103,22 +11186,22 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G311" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H311" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
@@ -11151,7 +11234,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -11160,18 +11243,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>378</v>
+        <v>388</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11186,22 +11269,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11219,7 +11302,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -11228,13 +11311,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11252,13 +11335,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>17</v>
@@ -11300,7 +11383,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11309,17 +11392,19 @@
         <v>57</v>
       </c>
       <c t="s" r="H318" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>19</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
-      <c r="M318" s="7"/>
+      <c t="s" r="M318" s="7">
+        <v>390</v>
+      </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
       <c t="s" r="A319" s="6">
@@ -11333,13 +11418,13 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G319" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H319" s="8">
         <v>57</v>
@@ -11348,7 +11433,7 @@
         <v>187</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
@@ -11359,14 +11444,14 @@
         <v>13</v>
       </c>
       <c r="B320" s="7">
-        <v>214</v>
+        <v>138</v>
       </c>
       <c t="s" r="C320" s="7">
         <v>14</v>
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11375,13 +11460,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H320" s="8">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>135</v>
+        <v>254</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>24</v>
+        <v>242</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11392,29 +11477,29 @@
         <v>13</v>
       </c>
       <c r="B321" s="7">
-        <v>213</v>
+        <v>147</v>
       </c>
       <c t="s" r="C321" s="7">
         <v>14</v>
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G321" s="8">
-        <v>219</v>
+        <v>35</v>
       </c>
       <c t="s" r="H321" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>106</v>
+        <v>232</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>189</v>
+        <v>277</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
@@ -11447,7 +11532,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -11456,18 +11541,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11482,22 +11567,22 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11515,7 +11600,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -11524,13 +11609,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>217</v>
+        <v>75</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11548,22 +11633,22 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11581,7 +11666,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11590,13 +11675,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11614,22 +11699,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11662,7 +11747,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11671,10 +11756,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H330" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>40</v>
@@ -11695,13 +11780,13 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G331" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="H331" s="8">
         <v>35</v>
@@ -11710,7 +11795,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11728,7 +11813,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11740,10 +11825,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -11761,7 +11846,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11773,10 +11858,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -11809,7 +11894,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11821,15 +11906,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -11844,7 +11929,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -11856,15 +11941,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -11879,7 +11964,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -11888,20 +11973,20 @@
         <v>35</v>
       </c>
       <c t="s" r="H337" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="I337" s="7">
         <v>36</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c t="s" r="K337" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -11916,25 +12001,25 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G338" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="H338" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>37</v>
       </c>
       <c t="s" r="K338" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
@@ -11953,7 +12038,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -11962,13 +12047,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11986,22 +12071,22 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12019,7 +12104,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12028,13 +12113,13 @@
         <v>35</v>
       </c>
       <c t="s" r="H341" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12052,22 +12137,22 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G342" s="8">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c t="s" r="H342" s="8">
         <v>35</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="J342" s="7">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
@@ -12100,7 +12185,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12109,10 +12194,10 @@
         <v>35</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>178</v>
@@ -12120,7 +12205,7 @@
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12135,13 +12220,13 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c t="s" r="H345" s="8">
         <v>35</v>
@@ -12153,11 +12238,11 @@
         <v>187</v>
       </c>
       <c t="s" r="K345" s="7">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>337</v>
+        <v>282</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12172,7 +12257,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12184,7 +12269,7 @@
         <v>72</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c t="s" r="J346" s="7">
         <v>74</v>
@@ -12205,7 +12290,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12217,10 +12302,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12238,7 +12323,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12253,7 +12338,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12271,7 +12356,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12283,10 +12368,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12319,7 +12404,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12331,15 +12416,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c t="s" r="J351" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12354,7 +12439,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
@@ -12363,13 +12448,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H352" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12387,19 +12472,19 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>69</v>
@@ -12420,7 +12505,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -12429,13 +12514,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12453,22 +12538,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12501,7 +12586,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12510,18 +12595,18 @@
         <v>30</v>
       </c>
       <c t="s" r="H357" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
       <c t="s" r="M357" s="7">
-        <v>398</v>
+        <v>409</v>
       </c>
     </row>
     <row r="358" ht="14.25" customHeight="1">
@@ -12536,13 +12621,13 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>72</v>
@@ -12551,7 +12636,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -12569,7 +12654,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12578,13 +12663,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>194</v>
+        <v>148</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12602,22 +12687,22 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12635,22 +12720,22 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c t="s" r="H361" s="8">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12683,13 +12768,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>57</v>
@@ -12698,7 +12783,7 @@
         <v>42</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12731,7 +12816,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12740,10 +12825,10 @@
         <v>57</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>40</v>
@@ -12764,13 +12849,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>57</v>
@@ -12779,7 +12864,7 @@
         <v>58</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
@@ -12797,7 +12882,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12806,13 +12891,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>25</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12830,13 +12915,13 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>57</v>
@@ -12845,7 +12930,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12863,7 +12948,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12872,13 +12957,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12896,22 +12981,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -12944,7 +13029,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -12953,18 +13038,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>406</v>
+        <v>417</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -12979,22 +13064,22 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>146</v>
+        <v>194</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -13012,7 +13097,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13021,13 +13106,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
@@ -13045,22 +13130,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13078,7 +13163,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
@@ -13090,7 +13175,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c t="s" r="J376" s="7">
         <v>43</v>
@@ -13111,7 +13196,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13123,10 +13208,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13159,7 +13244,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13168,18 +13253,18 @@
         <v>57</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>63</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13194,13 +13279,13 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>57</v>
@@ -13209,12 +13294,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
       <c t="s" r="M380" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="381" ht="14.25" customHeight="1">
@@ -13229,7 +13314,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13241,10 +13326,10 @@
         <v>35</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13262,7 +13347,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13274,7 +13359,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>24</v>
@@ -13295,7 +13380,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13304,13 +13389,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13328,13 +13413,13 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>57</v>
@@ -13343,7 +13428,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
@@ -13376,7 +13461,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F386" s="7">
         <v>321</v>
@@ -13385,17 +13470,19 @@
         <v>57</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>38</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
-      <c r="M386" s="7"/>
+      <c t="s" r="M386" s="7">
+        <v>421</v>
+      </c>
     </row>
     <row r="387" ht="14.25" customHeight="1">
       <c t="s" r="A387" s="6">
@@ -13409,13 +13496,13 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>57</v>
@@ -13424,7 +13511,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13442,7 +13529,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13454,10 +13541,10 @@
         <v>34</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13490,7 +13577,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13502,15 +13589,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -13525,7 +13612,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13558,7 +13645,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13591,7 +13678,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13603,10 +13690,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13624,7 +13711,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13633,13 +13720,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H394" s="8">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13657,19 +13744,19 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G395" s="8">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c t="s" r="H395" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>32</v>
@@ -13705,7 +13792,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F397" s="7">
         <v>321</v>
@@ -13717,15 +13804,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I397" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
       <c t="s" r="M397" s="7">
-        <v>413</v>
+        <v>425</v>
       </c>
     </row>
     <row r="398" ht="14.25" customHeight="1">
@@ -13740,7 +13827,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F398" s="7">
         <v>321</v>
@@ -13749,10 +13836,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>23</v>
@@ -13773,22 +13860,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="F399" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13817,11 +13904,11 @@
         <v>5805</v>
       </c>
       <c t="s" r="C401" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -13830,10 +13917,10 @@
         <v>72</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c t="s" r="J401" s="7">
         <v>51</v>
@@ -13841,7 +13928,7 @@
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -13852,26 +13939,26 @@
         <v>5806</v>
       </c>
       <c t="s" r="C402" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13904,7 +13991,7 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
@@ -13913,18 +14000,18 @@
         <v>72</v>
       </c>
       <c t="s" r="H404" s="8">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>419</v>
+        <v>431</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -13939,13 +14026,13 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G405" s="8">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c t="s" r="H405" s="8">
         <v>72</v>
@@ -13954,7 +14041,7 @@
         <v>23</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13987,27 +14074,27 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>53</v>
+        <v>435</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14022,7 +14109,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14034,7 +14121,7 @@
         <v>35</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>43</v>
@@ -14055,7 +14142,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -14067,10 +14154,10 @@
         <v>57</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14103,7 +14190,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14118,12 +14205,12 @@
         <v>47</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>424</v>
+        <v>437</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14138,7 +14225,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -14147,13 +14234,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>160</v>
+        <v>294</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14171,22 +14258,22 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>423</v>
+        <v>436</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c t="s" r="J413" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
@@ -14219,7 +14306,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -14231,15 +14318,15 @@
         <v>35</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -14254,7 +14341,7 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
@@ -14266,7 +14353,7 @@
         <v>57</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>40</v>
@@ -14287,7 +14374,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14299,10 +14386,10 @@
         <v>72</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14320,7 +14407,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
@@ -14329,13 +14416,13 @@
         <v>72</v>
       </c>
       <c t="s" r="H418" s="8">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14353,22 +14440,22 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="F419" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G419" s="8">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c t="s" r="H419" s="8">
         <v>72</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>
@@ -14401,7 +14488,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14410,13 +14497,13 @@
         <v>57</v>
       </c>
       <c t="s" r="H421" s="8">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14434,22 +14521,22 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G422" s="8">
-        <v>431</v>
+        <v>444</v>
       </c>
       <c t="s" r="H422" s="8">
         <v>57</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14457,7 +14544,7 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c t="s" r="A423" s="9">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="B423" s="9"/>
       <c r="C423" s="9"/>
@@ -14477,7 +14564,7 @@
     <row r="424" ht="65.25" customHeight="1"/>
     <row r="425" ht="17.25" customHeight="1">
       <c t="s" r="A425" s="10">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="B425" s="10"/>
       <c r="C425" s="10"/>
@@ -14490,7 +14577,7 @@
       <c r="J425" s="10"/>
       <c r="K425" s="10"/>
       <c t="s" r="L425" s="11">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="M425" s="11"/>
       <c r="N425" s="11"/>

--- a/Data/FlightPlan/FPL_16OCT26.xlsx
+++ b/Data/FlightPlan/FPL_16OCT26.xlsx
@@ -260,9 +260,6 @@
     <t>19:20</t>
   </si>
   <si>
-    <t>19:35</t>
-  </si>
-  <si>
     <t>20:20</t>
   </si>
   <si>
@@ -686,6 +683,9 @@
     <t>16:10</t>
   </si>
   <si>
+    <t>16:50</t>
+  </si>
+  <si>
     <t>16:40</t>
   </si>
   <si>
@@ -707,582 +707,582 @@
     <t>14:42</t>
   </si>
   <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>21:20</t>
+  </si>
+  <si>
+    <t>ICN</t>
+  </si>
+  <si>
+    <t>02:35</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>11:47</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>13:38</t>
+  </si>
+  <si>
+    <t>15:53</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>21:00</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>09:25</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>15:24</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>05:45</t>
+  </si>
+  <si>
+    <t>07:35</t>
+  </si>
+  <si>
+    <t>16:37</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>21:30</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>12:59</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>15:49</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>13:24</t>
+  </si>
+  <si>
+    <t>16:59</t>
+  </si>
+  <si>
     <t>17:40</t>
   </si>
   <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>16:27</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>16:18</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>11:26</t>
+  </si>
+  <si>
+    <t>13:53</t>
+  </si>
+  <si>
+    <t>15:57</t>
+  </si>
+  <si>
+    <t>VN-A630</t>
+  </si>
+  <si>
+    <t>15:17</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>08:44</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>14:32</t>
+  </si>
+  <si>
+    <t>17:17</t>
+  </si>
+  <si>
+    <t>19:15</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>10:57</t>
+  </si>
+  <si>
+    <t>15:09</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:02</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>VN-A635</t>
+  </si>
+  <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>17:29</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>00:20</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>17:02</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>02:10</t>
+  </si>
+  <si>
+    <t>03:00</t>
+  </si>
+  <si>
+    <t>04:35</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>06:36</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:57</t>
+  </si>
+  <si>
+    <t>10:52</t>
+  </si>
+  <si>
+    <t>12:53</t>
+  </si>
+  <si>
+    <t>16:01</t>
+  </si>
+  <si>
+    <t>20:55</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:11</t>
+  </si>
+  <si>
+    <t>11:06</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
     <t>19:40</t>
   </si>
   <si>
-    <t>ICN</t>
-  </si>
-  <si>
-    <t>02:35</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>11:47</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>13:38</t>
-  </si>
-  <si>
-    <t>15:53</t>
-  </si>
-  <si>
-    <t>VII</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>21:00</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>09:25</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>15:24</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>05:45</t>
-  </si>
-  <si>
-    <t>07:35</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>21:30</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>12:59</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>15:49</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>13:24</t>
-  </si>
-  <si>
-    <t>16:59</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>16:27</t>
-  </si>
-  <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>16:18</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>13:53</t>
-  </si>
-  <si>
-    <t>15:57</t>
-  </si>
-  <si>
-    <t>VN-A630</t>
-  </si>
-  <si>
-    <t>15:17</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>08:44</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>14:32</t>
-  </si>
-  <si>
-    <t>17:17</t>
-  </si>
-  <si>
-    <t>19:15</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>10:57</t>
-  </si>
-  <si>
-    <t>15:09</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:02</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>14:45</t>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>VN-A641</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>13:11</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:58</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>15:44</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>12:41</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>18:31</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>15:19</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HKG</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>18:54</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>13:29</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A650</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>05:20</t>
+  </si>
+  <si>
+    <t>07:13</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>15:26</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A651</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>10:05</t>
+  </si>
+  <si>
+    <t>13:42</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>02:00</t>
+  </si>
+  <si>
+    <t>06:10</t>
+  </si>
+  <si>
+    <t>VN-A656</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>15:27</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>04:50</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>13:51</t>
   </si>
   <si>
     <t>16:05</t>
   </si>
   <si>
-    <t>VN-A635</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>17:29</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>00:20</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>17:02</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>02:10</t>
-  </si>
-  <si>
-    <t>03:00</t>
-  </si>
-  <si>
-    <t>04:35</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>06:36</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:57</t>
-  </si>
-  <si>
-    <t>10:52</t>
-  </si>
-  <si>
-    <t>12:53</t>
-  </si>
-  <si>
-    <t>16:01</t>
-  </si>
-  <si>
-    <t>20:55</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:11</t>
-  </si>
-  <si>
-    <t>11:06</t>
-  </si>
-  <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>21:20</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>VN-A641</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>13:11</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:58</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>15:44</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>12:41</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>18:31</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>15:19</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HKG</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>18:54</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>13:29</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A650</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>05:20</t>
-  </si>
-  <si>
-    <t>07:13</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>15:26</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A651</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>10:05</t>
-  </si>
-  <si>
-    <t>13:42</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>02:00</t>
-  </si>
-  <si>
-    <t>06:10</t>
-  </si>
-  <si>
-    <t>VN-A656</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>12:48</t>
-  </si>
-  <si>
-    <t>15:27</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>04:50</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>13:51</t>
-  </si>
-  <si>
     <t>16:36</t>
   </si>
   <si>
@@ -1298,6 +1298,9 @@
     <t>17:15</t>
   </si>
   <si>
+    <t>17:24</t>
+  </si>
+  <si>
     <t>VN-A661</t>
   </si>
   <si>
@@ -1412,9 +1415,6 @@
     <t>17:07</t>
   </si>
   <si>
-    <t>20:00</t>
-  </si>
-  <si>
     <t>02:15</t>
   </si>
   <si>
@@ -1544,7 +1544,7 @@
     <t>Total Record(s): 340</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 16, 2026 15:34</t>
+    <t xml:space="preserve">Generated on  Oct 16, 2026 15:49</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="L31" s="7"/>
       <c t="s" r="M31" s="7">
-        <v>83</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" ht="14.25" customHeight="1">
@@ -2884,17 +2884,17 @@
         <v>76</v>
       </c>
       <c t="s" r="I32" s="7">
+        <v>83</v>
+      </c>
+      <c t="s" r="J32" s="7">
         <v>84</v>
       </c>
-      <c t="s" r="J32" s="7">
+      <c t="s" r="K32" s="7">
         <v>85</v>
-      </c>
-      <c t="s" r="K32" s="7">
-        <v>86</v>
       </c>
       <c r="L32" s="7"/>
       <c t="s" r="M32" s="7">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" ht="14.25" customHeight="1">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="D34" s="7"/>
       <c t="s" r="E34" s="7">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F34" s="7">
         <v>321</v>
@@ -2933,18 +2933,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H34" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I34" s="7">
         <v>89</v>
       </c>
-      <c t="s" r="I34" s="7">
+      <c t="s" r="J34" s="7">
         <v>90</v>
-      </c>
-      <c t="s" r="J34" s="7">
-        <v>91</v>
       </c>
       <c r="K34" s="7"/>
       <c r="L34" s="7"/>
       <c t="s" r="M34" s="7">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2959,22 +2959,22 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
+        <v>87</v>
+      </c>
+      <c r="F35" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G35" s="8">
         <v>88</v>
-      </c>
-      <c r="F35" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G35" s="8">
-        <v>89</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I35" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J35" s="7">
         <v>92</v>
-      </c>
-      <c t="s" r="J35" s="7">
-        <v>93</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -3004,10 +3004,10 @@
         <v>39</v>
       </c>
       <c t="s" r="I36" s="7">
+        <v>93</v>
+      </c>
+      <c t="s" r="J36" s="7">
         <v>94</v>
-      </c>
-      <c t="s" r="J36" s="7">
-        <v>95</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -3040,27 +3040,27 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
+        <v>95</v>
+      </c>
+      <c r="F38" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G38" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H38" s="8">
         <v>96</v>
       </c>
-      <c r="F38" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G38" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H38" s="8">
+      <c t="s" r="I38" s="7">
         <v>97</v>
       </c>
-      <c t="s" r="I38" s="7">
+      <c t="s" r="J38" s="7">
         <v>98</v>
-      </c>
-      <c t="s" r="J38" s="7">
-        <v>99</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
       <c t="s" r="M38" s="7">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="39" ht="14.25" customHeight="1">
@@ -3075,19 +3075,19 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
+        <v>95</v>
+      </c>
+      <c r="F39" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G39" s="8">
         <v>96</v>
       </c>
-      <c r="F39" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G39" s="8">
-        <v>97</v>
-      </c>
       <c t="s" r="H39" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c t="s" r="J39" s="7">
         <v>31</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D40" s="7"/>
       <c t="s" r="E40" s="7">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F40" s="7">
         <v>321</v>
@@ -3120,10 +3120,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I40" s="7">
+        <v>100</v>
+      </c>
+      <c t="s" r="J40" s="7">
         <v>101</v>
-      </c>
-      <c t="s" r="J40" s="7">
-        <v>102</v>
       </c>
       <c r="K40" s="7"/>
       <c r="L40" s="7"/>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -3150,10 +3150,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H41" s="8">
+        <v>102</v>
+      </c>
+      <c t="s" r="I41" s="7">
         <v>103</v>
-      </c>
-      <c t="s" r="I41" s="7">
-        <v>104</v>
       </c>
       <c t="s" r="J41" s="7">
         <v>74</v>
@@ -3185,11 +3185,11 @@
         <v>2869</v>
       </c>
       <c t="s" r="C43" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3198,18 +3198,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H43" s="8">
+        <v>106</v>
+      </c>
+      <c t="s" r="I43" s="7">
         <v>107</v>
       </c>
-      <c t="s" r="I43" s="7">
+      <c t="s" r="J43" s="7">
         <v>108</v>
-      </c>
-      <c t="s" r="J43" s="7">
-        <v>109</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
       <c t="s" r="M43" s="7">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="44" ht="14.25" customHeight="1">
@@ -3224,13 +3224,13 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
+        <v>105</v>
+      </c>
+      <c r="F44" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G44" s="8">
         <v>106</v>
-      </c>
-      <c r="F44" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G44" s="8">
-        <v>107</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>60</v>
@@ -3244,7 +3244,7 @@
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
       <c t="s" r="M44" s="7">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3259,7 +3259,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3271,15 +3271,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I45" s="7">
+        <v>111</v>
+      </c>
+      <c t="s" r="J45" s="7">
         <v>112</v>
-      </c>
-      <c t="s" r="J45" s="7">
-        <v>113</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
       <c t="s" r="M45" s="7">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="46" ht="14.25" customHeight="1">
@@ -3290,11 +3290,11 @@
         <v>5068</v>
       </c>
       <c t="s" r="C46" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3303,20 +3303,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H46" s="8">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c t="s" r="I46" s="7">
         <v>30</v>
       </c>
       <c t="s" r="J46" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c t="s" r="K46" s="7">
         <v>46</v>
       </c>
       <c r="L46" s="7"/>
       <c t="s" r="M46" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" ht="14.25" customHeight="1">
@@ -3327,33 +3327,33 @@
         <v>5069</v>
       </c>
       <c t="s" r="C47" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D47" s="7"/>
       <c t="s" r="E47" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F47" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G47" s="8">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c t="s" r="H47" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I47" s="7">
+        <v>116</v>
+      </c>
+      <c t="s" r="J47" s="7">
         <v>117</v>
       </c>
-      <c t="s" r="J47" s="7">
+      <c t="s" r="K47" s="7">
         <v>118</v>
-      </c>
-      <c t="s" r="K47" s="7">
-        <v>119</v>
       </c>
       <c r="L47" s="7"/>
       <c t="s" r="M47" s="7">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="48" ht="14.25" customHeight="1">
@@ -3364,11 +3364,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C48" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3377,20 +3377,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H48" s="8">
+        <v>120</v>
+      </c>
+      <c t="s" r="I48" s="7">
         <v>121</v>
       </c>
-      <c t="s" r="I48" s="7">
+      <c t="s" r="J48" s="7">
         <v>122</v>
       </c>
-      <c t="s" r="J48" s="7">
+      <c t="s" r="K48" s="7">
         <v>123</v>
-      </c>
-      <c t="s" r="K48" s="7">
-        <v>124</v>
       </c>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3420,22 +3420,22 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
+        <v>125</v>
+      </c>
+      <c r="F50" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G50" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H50" s="8">
         <v>126</v>
       </c>
-      <c r="F50" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G50" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H50" s="8">
+      <c t="s" r="I50" s="7">
         <v>127</v>
       </c>
-      <c t="s" r="I50" s="7">
-        <v>128</v>
-      </c>
       <c t="s" r="J50" s="7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3455,27 +3455,27 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
+        <v>125</v>
+      </c>
+      <c r="F51" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G51" s="8">
         <v>126</v>
       </c>
-      <c r="F51" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G51" s="8">
-        <v>127</v>
-      </c>
       <c t="s" r="H51" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
       <c t="s" r="M51" s="7">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="52" ht="14.25" customHeight="1">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3499,13 +3499,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H52" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I52" s="7">
+        <v>130</v>
+      </c>
+      <c t="s" r="J52" s="7">
         <v>131</v>
-      </c>
-      <c t="s" r="J52" s="7">
-        <v>132</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3525,13 +3525,13 @@
       </c>
       <c r="D53" s="7"/>
       <c t="s" r="E53" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G53" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H53" s="8">
         <v>60</v>
@@ -3543,11 +3543,11 @@
         <v>61</v>
       </c>
       <c t="s" r="K53" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L53" s="7"/>
       <c t="s" r="M53" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="54" ht="14.25" customHeight="1">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3574,10 +3574,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
@@ -3607,10 +3607,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I55" s="7">
+        <v>135</v>
+      </c>
+      <c t="s" r="J55" s="7">
         <v>136</v>
-      </c>
-      <c t="s" r="J55" s="7">
-        <v>137</v>
       </c>
       <c r="K55" s="7"/>
       <c r="L55" s="7"/>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3640,10 +3640,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I56" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="J56" s="7">
         <v>138</v>
-      </c>
-      <c t="s" r="J56" s="7">
-        <v>139</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3685,18 +3685,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H58" s="8">
+        <v>140</v>
+      </c>
+      <c t="s" r="I58" s="7">
         <v>141</v>
       </c>
-      <c t="s" r="I58" s="7">
+      <c t="s" r="J58" s="7">
         <v>142</v>
-      </c>
-      <c t="s" r="J58" s="7">
-        <v>143</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
       <c t="s" r="M58" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="59" ht="14.25" customHeight="1">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
@@ -3735,18 +3735,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H60" s="8">
+        <v>145</v>
+      </c>
+      <c t="s" r="I60" s="7">
         <v>146</v>
       </c>
-      <c t="s" r="I60" s="7">
+      <c t="s" r="J60" s="7">
         <v>147</v>
-      </c>
-      <c t="s" r="J60" s="7">
-        <v>148</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
       <c t="s" r="M60" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="61" ht="14.25" customHeight="1">
@@ -3761,27 +3761,27 @@
       </c>
       <c r="D61" s="7"/>
       <c t="s" r="E61" s="7">
+        <v>144</v>
+      </c>
+      <c r="F61" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G61" s="8">
         <v>145</v>
-      </c>
-      <c r="F61" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G61" s="8">
-        <v>146</v>
       </c>
       <c t="s" r="H61" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I61" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J61" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="K61" s="7"/>
       <c r="L61" s="7"/>
       <c t="s" r="M61" s="7">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="62" ht="14.25" customHeight="1">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3805,18 +3805,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H62" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J62" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3831,22 +3831,22 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G63" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H63" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I63" s="7">
+        <v>153</v>
+      </c>
+      <c t="s" r="J63" s="7">
         <v>154</v>
-      </c>
-      <c t="s" r="J63" s="7">
-        <v>155</v>
       </c>
       <c r="K63" s="7"/>
       <c r="L63" s="7"/>
@@ -3864,7 +3864,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3876,7 +3876,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c t="s" r="J64" s="7">
         <v>33</v>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3909,10 +3909,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I65" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J65" s="7">
         <v>157</v>
-      </c>
-      <c t="s" r="J65" s="7">
-        <v>158</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3942,10 +3942,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I66" s="7">
+        <v>158</v>
+      </c>
+      <c t="s" r="J66" s="7">
         <v>159</v>
-      </c>
-      <c t="s" r="J66" s="7">
-        <v>160</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3978,27 +3978,27 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
+        <v>160</v>
+      </c>
+      <c r="F68" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G68" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H68" s="8">
         <v>161</v>
       </c>
-      <c r="F68" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G68" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H68" s="8">
+      <c t="s" r="I68" s="7">
         <v>162</v>
       </c>
-      <c t="s" r="I68" s="7">
-        <v>163</v>
-      </c>
       <c t="s" r="J68" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4013,27 +4013,27 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
+        <v>160</v>
+      </c>
+      <c r="F69" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G69" s="8">
         <v>161</v>
       </c>
-      <c r="F69" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G69" s="8">
-        <v>162</v>
-      </c>
       <c t="s" r="H69" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4048,7 +4048,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4057,18 +4057,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I70" s="7">
+        <v>107</v>
+      </c>
+      <c t="s" r="J70" s="7">
         <v>108</v>
-      </c>
-      <c t="s" r="J70" s="7">
-        <v>109</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4083,19 +4083,19 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H71" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>44</v>
@@ -4103,7 +4103,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4130,7 +4130,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>82</v>
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4160,13 +4160,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H73" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I73" s="7">
         <v>33</v>
       </c>
       <c t="s" r="J73" s="7">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4184,22 +4184,22 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H74" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4232,27 +4232,27 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
+        <v>171</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H76" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I76" s="7">
         <v>172</v>
       </c>
-      <c r="F76" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G76" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H76" s="8">
-        <v>97</v>
-      </c>
-      <c t="s" r="I76" s="7">
+      <c t="s" r="J76" s="7">
         <v>173</v>
-      </c>
-      <c t="s" r="J76" s="7">
-        <v>174</v>
       </c>
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4267,13 +4267,13 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H77" s="8">
         <v>60</v>
@@ -4282,12 +4282,12 @@
         <v>50</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4314,15 +4314,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I78" s="7">
+        <v>176</v>
+      </c>
+      <c t="s" r="J78" s="7">
         <v>177</v>
-      </c>
-      <c t="s" r="J78" s="7">
-        <v>178</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4349,15 +4349,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I79" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J79" s="7">
         <v>180</v>
-      </c>
-      <c t="s" r="J79" s="7">
-        <v>181</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
@@ -4381,13 +4381,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4405,13 +4405,13 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G81" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H81" s="8">
         <v>28</v>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="D82" s="7"/>
       <c t="s" r="E82" s="7">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F82" s="7">
         <v>321</v>
@@ -4450,17 +4450,17 @@
         <v>60</v>
       </c>
       <c t="s" r="I82" s="7">
+        <v>183</v>
+      </c>
+      <c t="s" r="J82" s="7">
         <v>184</v>
       </c>
-      <c t="s" r="J82" s="7">
+      <c t="s" r="K82" s="7">
         <v>185</v>
-      </c>
-      <c t="s" r="K82" s="7">
-        <v>186</v>
       </c>
       <c r="L82" s="7"/>
       <c t="s" r="M82" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
@@ -4490,29 +4490,29 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
+        <v>186</v>
+      </c>
+      <c r="F84" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G84" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H84" s="8">
+        <v>88</v>
+      </c>
+      <c t="s" r="I84" s="7">
         <v>187</v>
-      </c>
-      <c r="F84" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G84" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H84" s="8">
-        <v>89</v>
-      </c>
-      <c t="s" r="I84" s="7">
-        <v>188</v>
       </c>
       <c t="s" r="J84" s="7">
         <v>78</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4527,13 +4527,13 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c t="s" r="H85" s="8">
         <v>60</v>
@@ -4542,14 +4542,14 @@
         <v>81</v>
       </c>
       <c t="s" r="J85" s="7">
+        <v>190</v>
+      </c>
+      <c t="s" r="K85" s="7">
         <v>191</v>
-      </c>
-      <c t="s" r="K85" s="7">
-        <v>192</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
@@ -4573,13 +4573,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H86" s="8">
+        <v>193</v>
+      </c>
+      <c t="s" r="I86" s="7">
         <v>194</v>
       </c>
-      <c t="s" r="I86" s="7">
+      <c t="s" r="J86" s="7">
         <v>195</v>
-      </c>
-      <c t="s" r="J86" s="7">
-        <v>196</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4597,22 +4597,22 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4654,13 +4654,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H89" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4680,19 +4680,19 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>44</v>
@@ -4700,7 +4700,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
@@ -4724,20 +4724,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J91" s="7">
         <v>25</v>
       </c>
       <c t="s" r="K91" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -4752,29 +4752,29 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J92" s="7">
+        <v>202</v>
+      </c>
+      <c t="s" r="K92" s="7">
         <v>203</v>
-      </c>
-      <c t="s" r="K92" s="7">
-        <v>204</v>
       </c>
       <c r="L92" s="7"/>
       <c t="s" r="M92" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="93" ht="14.25" customHeight="1">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
@@ -4801,10 +4801,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I93" s="7">
+        <v>204</v>
+      </c>
+      <c t="s" r="J93" s="7">
         <v>205</v>
-      </c>
-      <c t="s" r="J93" s="7">
-        <v>206</v>
       </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
@@ -4837,7 +4837,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4849,15 +4849,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I95" s="7">
+        <v>207</v>
+      </c>
+      <c t="s" r="J95" s="7">
         <v>208</v>
-      </c>
-      <c t="s" r="J95" s="7">
-        <v>209</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4884,7 +4884,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>44</v>
@@ -4892,7 +4892,7 @@
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -4919,15 +4919,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I97" s="7">
+        <v>212</v>
+      </c>
+      <c t="s" r="J97" s="7">
         <v>213</v>
-      </c>
-      <c t="s" r="J97" s="7">
-        <v>214</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4954,10 +4954,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I98" s="7">
+        <v>215</v>
+      </c>
+      <c t="s" r="J98" s="7">
         <v>216</v>
-      </c>
-      <c t="s" r="J98" s="7">
-        <v>217</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4975,7 +4975,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4987,10 +4987,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -5020,7 +5020,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c t="s" r="J100" s="7">
         <v>37</v>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5068,15 +5068,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5103,7 +5103,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="J103" s="7">
         <v>22</v>
@@ -5111,7 +5111,7 @@
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5138,10 +5138,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -5161,7 +5161,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5176,11 +5176,13 @@
         <v>23</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
+      <c t="s" r="M105" s="7">
+        <v>224</v>
+      </c>
     </row>
     <row r="106" ht="14.25" customHeight="1">
       <c t="s" r="A106" s="6">
@@ -5194,7 +5196,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5203,13 +5205,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="I106" s="7">
         <v>225</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5227,19 +5229,19 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J107" s="7">
         <v>226</v>
@@ -5322,7 +5324,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>61</v>
@@ -5357,10 +5359,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5371,7 +5373,7 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c t="s" r="C112" s="7">
         <v>14</v>
@@ -5387,13 +5389,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>233</v>
+        <v>82</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5404,7 +5406,7 @@
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c t="s" r="C113" s="7">
         <v>14</v>
@@ -5417,16 +5419,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>97</v>
+        <v>232</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>170</v>
+        <v>233</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5577,7 +5579,7 @@
         <v>79</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5609,10 +5611,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5645,7 +5647,7 @@
         <v>246</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5731,7 +5733,7 @@
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c t="s" r="M123" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" ht="14.25" customHeight="1">
@@ -5758,7 +5760,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I124" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J124" s="7">
         <v>54</v>
@@ -5808,15 +5810,15 @@
         <v>60</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -5840,7 +5842,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>253</v>
@@ -5874,13 +5876,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>234</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="J128" s="7">
         <v>257</v>
@@ -5947,7 +5949,7 @@
         <v>5068</v>
       </c>
       <c t="s" r="C131" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
@@ -5966,7 +5968,7 @@
         <v>81</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5998,7 +6000,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>73</v>
@@ -6034,27 +6036,27 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
+        <v>262</v>
+      </c>
+      <c r="F134" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G134" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H134" s="8">
         <v>263</v>
       </c>
-      <c r="F134" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G134" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H134" s="8">
-        <v>264</v>
-      </c>
       <c t="s" r="I134" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6069,27 +6071,27 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
+        <v>262</v>
+      </c>
+      <c r="F135" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G135" s="8">
         <v>263</v>
       </c>
-      <c r="F135" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G135" s="8">
+      <c t="s" r="H135" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I135" s="7">
         <v>264</v>
       </c>
-      <c t="s" r="H135" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I135" s="7">
+      <c t="s" r="J135" s="7">
         <v>265</v>
-      </c>
-      <c t="s" r="J135" s="7">
-        <v>266</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6104,7 +6106,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6116,7 +6118,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="J136" s="7">
         <v>31</v>
@@ -6137,7 +6139,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -6152,7 +6154,7 @@
         <v>82</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -6170,7 +6172,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -6182,10 +6184,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I138" s="7">
+        <v>268</v>
+      </c>
+      <c t="s" r="J138" s="7">
         <v>269</v>
-      </c>
-      <c t="s" r="J138" s="7">
-        <v>270</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6214,31 +6216,31 @@
         <v>7615</v>
       </c>
       <c t="s" r="C140" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
+        <v>270</v>
+      </c>
+      <c r="F140" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G140" s="8">
         <v>271</v>
-      </c>
-      <c r="F140" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G140" s="8">
-        <v>272</v>
       </c>
       <c t="s" r="H140" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c t="s" r="M140" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" ht="14.25" customHeight="1">
@@ -6249,11 +6251,11 @@
         <v>7615</v>
       </c>
       <c t="s" r="C141" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6265,15 +6267,15 @@
         <v>76</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6284,11 +6286,11 @@
         <v>7706</v>
       </c>
       <c t="s" r="C142" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6300,17 +6302,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>58</v>
       </c>
       <c t="s" r="K142" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6340,7 +6342,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6352,15 +6354,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6375,7 +6377,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6387,17 +6389,17 @@
         <v>60</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c t="s" r="K145" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6412,7 +6414,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6427,10 +6429,10 @@
         <v>27</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c t="s" r="K146" s="7">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c r="L146" s="7"/>
       <c t="s" r="M146" s="7">
@@ -6449,7 +6451,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6461,10 +6463,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c t="s" r="K147" s="7">
         <v>282</v>
@@ -6486,7 +6488,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6504,7 +6506,7 @@
         <v>285</v>
       </c>
       <c t="s" r="K148" s="7">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
@@ -6550,10 +6552,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6585,7 +6587,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>56</v>
@@ -6737,7 +6739,7 @@
         <v>295</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6772,7 +6774,7 @@
         <v>297</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6817,10 +6819,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6919,7 +6921,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>23</v>
@@ -6951,16 +6953,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I163" s="7">
+        <v>90</v>
+      </c>
+      <c t="s" r="J163" s="7">
         <v>91</v>
-      </c>
-      <c t="s" r="J163" s="7">
-        <v>92</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -7005,15 +7007,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7040,7 +7042,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>254</v>
@@ -7087,7 +7089,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I168" s="7">
         <v>67</v>
@@ -7119,7 +7121,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>28</v>
@@ -7157,13 +7159,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>311</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c t="s" r="K170" s="7">
         <v>22</v>
@@ -7191,7 +7193,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>28</v>
@@ -7203,7 +7205,7 @@
         <v>27</v>
       </c>
       <c t="s" r="K171" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
@@ -7234,13 +7236,13 @@
         <v>228</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c t="s" r="J172" s="7">
         <v>314</v>
       </c>
       <c t="s" r="K172" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
@@ -7271,17 +7273,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c t="s" r="K173" s="7">
         <v>33</v>
       </c>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7323,10 +7325,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -7358,10 +7360,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7393,10 +7395,10 @@
         <v>234</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7444,7 +7446,7 @@
         <v>319</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7473,7 +7475,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I180" s="7">
         <v>300</v>
@@ -7505,7 +7507,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H181" s="8">
         <v>60</v>
@@ -7514,7 +7516,7 @@
         <v>229</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7546,10 +7548,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7584,14 +7586,14 @@
         <v>81</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="K183" s="7">
         <v>324</v>
       </c>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>325</v>
+        <v>30</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7654,19 +7656,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
+        <v>325</v>
+      </c>
+      <c r="F186" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G186" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H186" s="8">
         <v>326</v>
       </c>
-      <c r="F186" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G186" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H186" s="8">
+      <c t="s" r="I186" s="7">
         <v>327</v>
-      </c>
-      <c t="s" r="I186" s="7">
-        <v>328</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>79</v>
@@ -7674,7 +7676,7 @@
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7689,19 +7691,19 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
+        <v>325</v>
+      </c>
+      <c r="F187" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G187" s="8">
         <v>326</v>
       </c>
-      <c r="F187" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G187" s="8">
-        <v>327</v>
-      </c>
       <c t="s" r="H187" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="J187" s="7">
         <v>56</v>
@@ -7709,7 +7711,7 @@
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7724,7 +7726,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7739,7 +7741,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7757,7 +7759,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7769,7 +7771,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>282</v>
@@ -7790,7 +7792,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7823,7 +7825,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -7835,10 +7837,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I191" s="7">
+        <v>329</v>
+      </c>
+      <c t="s" r="J191" s="7">
         <v>330</v>
-      </c>
-      <c t="s" r="J191" s="7">
-        <v>331</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7871,7 +7873,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7880,18 +7882,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c t="s" r="I193" s="7">
         <v>53</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7906,27 +7908,27 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G194" s="8">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c t="s" r="H194" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7941,7 +7943,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7950,13 +7952,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H195" s="8">
+        <v>333</v>
+      </c>
+      <c t="s" r="I195" s="7">
         <v>334</v>
       </c>
-      <c t="s" r="I195" s="7">
+      <c t="s" r="J195" s="7">
         <v>335</v>
-      </c>
-      <c t="s" r="J195" s="7">
-        <v>336</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7974,22 +7976,22 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c t="s" r="H196" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I196" s="7">
+        <v>336</v>
+      </c>
+      <c t="s" r="J196" s="7">
         <v>337</v>
-      </c>
-      <c t="s" r="J196" s="7">
-        <v>338</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -8022,7 +8024,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8034,15 +8036,15 @@
         <v>245</v>
       </c>
       <c t="s" r="I198" s="7">
+        <v>339</v>
+      </c>
+      <c t="s" r="J198" s="7">
         <v>340</v>
-      </c>
-      <c t="s" r="J198" s="7">
-        <v>341</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8057,7 +8059,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8069,15 +8071,15 @@
         <v>228</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8092,7 +8094,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -8104,15 +8106,15 @@
         <v>245</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8127,7 +8129,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8139,15 +8141,15 @@
         <v>60</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8162,7 +8164,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8171,18 +8173,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8197,22 +8199,22 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -8230,7 +8232,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8242,10 +8244,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8263,7 +8265,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8275,10 +8277,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I205" s="7">
+        <v>348</v>
+      </c>
+      <c t="s" r="J205" s="7">
         <v>349</v>
-      </c>
-      <c t="s" r="J205" s="7">
-        <v>350</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8311,7 +8313,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8323,15 +8325,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I207" s="7">
+        <v>351</v>
+      </c>
+      <c t="s" r="J207" s="7">
         <v>352</v>
-      </c>
-      <c t="s" r="J207" s="7">
-        <v>353</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8346,7 +8348,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8358,7 +8360,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>77</v>
@@ -8366,7 +8368,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8381,7 +8383,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8390,10 +8392,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="J209" s="7">
         <v>241</v>
@@ -8401,7 +8403,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8416,29 +8418,29 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H210" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I210" s="7">
+        <v>142</v>
+      </c>
+      <c t="s" r="J210" s="7">
+        <v>151</v>
+      </c>
+      <c t="s" r="K210" s="7">
         <v>97</v>
-      </c>
-      <c t="s" r="I210" s="7">
-        <v>143</v>
-      </c>
-      <c t="s" r="J210" s="7">
-        <v>152</v>
-      </c>
-      <c t="s" r="K210" s="7">
-        <v>98</v>
       </c>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8453,22 +8455,22 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I211" s="7">
+        <v>153</v>
+      </c>
+      <c t="s" r="J211" s="7">
         <v>154</v>
-      </c>
-      <c t="s" r="J211" s="7">
-        <v>155</v>
       </c>
       <c t="s" r="K211" s="7">
         <v>26</v>
@@ -8490,19 +8492,19 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H212" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="J212" s="7">
         <v>82</v>
@@ -8512,7 +8514,7 @@
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8542,7 +8544,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8554,10 +8556,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8577,7 +8579,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8589,10 +8591,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
@@ -8603,14 +8605,14 @@
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8619,50 +8621,58 @@
         <v>60</v>
       </c>
       <c t="s" r="H216" s="8">
+        <v>96</v>
+      </c>
+      <c t="s" r="I216" s="7">
+        <v>281</v>
+      </c>
+      <c t="s" r="J216" s="7">
+        <v>359</v>
+      </c>
+      <c t="s" r="K216" s="7">
+        <v>46</v>
+      </c>
+      <c r="L216" s="7"/>
+      <c t="s" r="M216" s="7">
         <v>360</v>
       </c>
-      <c t="s" r="I216" s="7">
-        <v>217</v>
-      </c>
-      <c t="s" r="J216" s="7">
-        <v>82</v>
-      </c>
-      <c r="K216" s="7"/>
-      <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>360</v>
+        <v>96</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>47</v>
+        <v>183</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>361</v>
-      </c>
-      <c r="K217" s="7"/>
+        <v>169</v>
+      </c>
+      <c t="s" r="K217" s="7">
+        <v>291</v>
+      </c>
       <c r="L217" s="7"/>
-      <c r="M217" s="7"/>
+      <c t="s" r="M217" s="7">
+        <v>137</v>
+      </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
       <c t="s" r="A218" s="6">
@@ -8676,7 +8686,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8688,10 +8698,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8724,7 +8734,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8736,7 +8746,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>37</v>
@@ -8744,7 +8754,7 @@
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -8759,7 +8769,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8771,13 +8781,13 @@
         <v>17</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>300</v>
       </c>
       <c t="s" r="K221" s="7">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L221" s="7"/>
       <c t="s" r="M221" s="7">
@@ -8796,7 +8806,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8811,14 +8821,14 @@
         <v>40</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="K222" s="7">
         <v>236</v>
       </c>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8833,7 +8843,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8845,17 +8855,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K223" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8870,7 +8880,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8882,7 +8892,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>81</v>
@@ -8907,7 +8917,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8916,13 +8926,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8940,22 +8950,22 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c t="s" r="H226" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I226" s="7">
+        <v>367</v>
+      </c>
+      <c t="s" r="J226" s="7">
         <v>368</v>
-      </c>
-      <c t="s" r="J226" s="7">
-        <v>369</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8973,7 +8983,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8982,7 +8992,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H227" s="8">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c t="s" r="I227" s="7">
         <v>292</v>
@@ -9006,22 +9016,22 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c t="s" r="H228" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -9054,7 +9064,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -9063,10 +9073,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c t="s" r="J230" s="7">
         <v>300</v>
@@ -9074,7 +9084,7 @@
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
       <c t="s" r="M230" s="7">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="231" ht="14.25" customHeight="1">
@@ -9089,13 +9099,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>60</v>
@@ -9104,7 +9114,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -9124,7 +9134,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9136,7 +9146,7 @@
         <v>245</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>25</v>
@@ -9144,7 +9154,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9159,7 +9169,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9171,10 +9181,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -9207,27 +9217,27 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
+        <v>375</v>
+      </c>
+      <c r="F235" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G235" s="8">
         <v>376</v>
-      </c>
-      <c r="F235" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G235" s="8">
-        <v>377</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c t="s" r="M235" s="7">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="236" ht="14.25" customHeight="1">
@@ -9242,7 +9252,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9251,7 +9261,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>253</v>
@@ -9262,7 +9272,7 @@
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9277,13 +9287,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>28</v>
@@ -9292,7 +9302,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -9310,7 +9320,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9358,7 +9368,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9367,18 +9377,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c t="s" r="M240" s="7">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="241" ht="14.25" customHeight="1">
@@ -9393,13 +9403,13 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>17</v>
@@ -9426,7 +9436,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9438,10 +9448,10 @@
         <v>21</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -9459,7 +9469,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9471,10 +9481,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
@@ -9492,7 +9502,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9504,7 +9514,7 @@
         <v>234</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c t="s" r="J244" s="7">
         <v>319</v>
@@ -9540,7 +9550,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9552,15 +9562,15 @@
         <v>60</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c t="s" r="M246" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="247" ht="14.25" customHeight="1">
@@ -9575,27 +9585,27 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
+        <v>384</v>
+      </c>
+      <c r="F247" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G247" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H247" s="8">
         <v>385</v>
       </c>
-      <c r="F247" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G247" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H247" s="8">
+      <c t="s" r="I247" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J247" s="7">
         <v>386</v>
-      </c>
-      <c t="s" r="I247" s="7">
-        <v>192</v>
-      </c>
-      <c t="s" r="J247" s="7">
-        <v>387</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
       <c t="s" r="M247" s="7">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="248" ht="14.25" customHeight="1">
@@ -9610,13 +9620,13 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
+        <v>384</v>
+      </c>
+      <c r="F248" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G248" s="8">
         <v>385</v>
-      </c>
-      <c r="F248" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G248" s="8">
-        <v>386</v>
       </c>
       <c t="s" r="H248" s="8">
         <v>60</v>
@@ -9625,7 +9635,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9643,7 +9653,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9655,7 +9665,7 @@
         <v>52</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>53</v>
@@ -9691,7 +9701,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9703,10 +9713,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9724,7 +9734,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9757,7 +9767,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9790,7 +9800,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9802,10 +9812,10 @@
         <v>234</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9838,7 +9848,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9850,7 +9860,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>78</v>
@@ -9858,7 +9868,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -9873,7 +9883,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9882,18 +9892,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c t="s" r="I257" s="7">
         <v>81</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -9908,22 +9918,22 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9956,7 +9966,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9968,7 +9978,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c t="s" r="J260" s="7">
         <v>44</v>
@@ -9976,7 +9986,7 @@
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -9991,7 +10001,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10011,7 +10021,7 @@
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c t="s" r="M261" s="7">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="262" ht="14.25" customHeight="1">
@@ -10026,7 +10036,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10038,10 +10048,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10059,7 +10069,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -10068,10 +10078,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c t="s" r="J263" s="7">
         <v>53</v>
@@ -10107,7 +10117,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
@@ -10116,18 +10126,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H265" s="8">
+        <v>397</v>
+      </c>
+      <c t="s" r="I265" s="7">
         <v>398</v>
       </c>
-      <c t="s" r="I265" s="7">
-        <v>399</v>
-      </c>
       <c t="s" r="J265" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10142,13 +10152,13 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>60</v>
@@ -10157,7 +10167,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -10177,7 +10187,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
@@ -10189,15 +10199,15 @@
         <v>245</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10212,7 +10222,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10227,7 +10237,7 @@
         <v>255</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10245,7 +10255,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
@@ -10254,13 +10264,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="I269" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -10278,22 +10288,22 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="H270" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -10311,7 +10321,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F271" s="7">
         <v>320</v>
@@ -10323,17 +10333,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>257</v>
       </c>
       <c t="s" r="K271" s="7">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="L271" s="7"/>
       <c t="s" r="M271" s="7">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="272" ht="14.25" customHeight="1">
@@ -10363,27 +10373,27 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
+        <v>404</v>
+      </c>
+      <c r="F273" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G273" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H273" s="8">
         <v>405</v>
-      </c>
-      <c r="F273" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G273" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H273" s="8">
-        <v>406</v>
       </c>
       <c t="s" r="I273" s="7">
         <v>307</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10398,27 +10408,27 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
+        <v>404</v>
+      </c>
+      <c r="F274" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G274" s="8">
         <v>405</v>
       </c>
-      <c r="F274" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G274" s="8">
-        <v>406</v>
-      </c>
       <c t="s" r="H274" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I274" s="7">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10433,7 +10443,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10442,7 +10452,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>81</v>
@@ -10453,7 +10463,7 @@
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10468,19 +10478,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>256</v>
@@ -10516,16 +10526,16 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
+        <v>408</v>
+      </c>
+      <c r="F278" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G278" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="H278" s="8">
         <v>409</v>
-      </c>
-      <c r="F278" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G278" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="H278" s="8">
-        <v>410</v>
       </c>
       <c t="s" r="I278" s="7">
         <v>56</v>
@@ -10549,22 +10559,22 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
+        <v>408</v>
+      </c>
+      <c r="F279" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G279" s="8">
         <v>409</v>
       </c>
-      <c r="F279" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G279" s="8">
+      <c t="s" r="H279" s="8">
+        <v>60</v>
+      </c>
+      <c t="s" r="I279" s="7">
         <v>410</v>
       </c>
-      <c t="s" r="H279" s="8">
-        <v>60</v>
-      </c>
-      <c t="s" r="I279" s="7">
+      <c t="s" r="J279" s="7">
         <v>411</v>
-      </c>
-      <c t="s" r="J279" s="7">
-        <v>412</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10597,7 +10607,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10609,15 +10619,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
       <c t="s" r="M281" s="7">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="282" ht="14.25" customHeight="1">
@@ -10632,7 +10642,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -10641,10 +10651,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H282" s="8">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J282" s="7">
         <v>42</v>
@@ -10652,7 +10662,7 @@
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -10667,27 +10677,27 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G283" s="8">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="H283" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I283" s="7">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -10702,7 +10712,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -10714,10 +10724,10 @@
         <v>238</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
@@ -10735,7 +10745,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -10747,10 +10757,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10768,7 +10778,7 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
@@ -10777,13 +10787,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c t="s" r="I286" s="7">
         <v>284</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10801,22 +10811,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I287" s="7">
+        <v>418</v>
+      </c>
+      <c t="s" r="J287" s="7">
         <v>419</v>
-      </c>
-      <c t="s" r="J287" s="7">
-        <v>420</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10849,7 +10859,7 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
@@ -10858,10 +10868,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H289" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c t="s" r="J289" s="7">
         <v>300</v>
@@ -10884,13 +10894,13 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G290" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H290" s="8">
         <v>17</v>
@@ -10899,12 +10909,12 @@
         <v>249</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10919,7 +10929,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -10928,20 +10938,20 @@
         <v>17</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c t="s" r="K291" s="7">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -10956,22 +10966,22 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c t="s" r="K292" s="7">
         <v>253</v>
@@ -10993,7 +11003,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11002,16 +11012,16 @@
         <v>28</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I293" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
@@ -11030,13 +11040,13 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G294" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H294" s="8">
         <v>28</v>
@@ -11045,14 +11055,14 @@
         <v>82</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c t="s" r="K294" s="7">
         <v>47</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11091,10 +11101,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c t="s" r="J296" s="7">
         <v>22</v>
@@ -11123,16 +11133,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -11161,17 +11171,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H298" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>428</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
-      <c r="M298" s="7"/>
+      <c t="s" r="M298" s="7">
+        <v>429</v>
+      </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
       <c t="s" r="A299" s="6">
@@ -11191,16 +11203,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G299" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H299" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
@@ -11233,7 +11245,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11242,18 +11254,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
       <c t="s" r="M301" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="302" ht="14.25" customHeight="1">
@@ -11268,13 +11280,13 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>60</v>
@@ -11283,12 +11295,12 @@
         <v>78</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11303,7 +11315,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -11312,13 +11324,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H303" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -11336,22 +11348,22 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G304" s="8">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c t="s" r="H304" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11384,7 +11396,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11396,7 +11408,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>309</v>
@@ -11404,7 +11416,7 @@
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
       <c t="s" r="M306" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="307" ht="14.25" customHeight="1">
@@ -11419,7 +11431,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11439,7 +11451,7 @@
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="308" ht="14.25" customHeight="1">
@@ -11454,7 +11466,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11474,7 +11486,7 @@
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11489,7 +11501,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11498,17 +11510,19 @@
         <v>60</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>428</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
-      <c r="M309" s="7"/>
+      <c t="s" r="M309" s="7">
+        <v>281</v>
+      </c>
     </row>
     <row r="310" ht="15" customHeight="1">
       <c t="s" r="A310" s="6">
@@ -11522,22 +11536,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -11570,7 +11584,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F312" s="7">
         <v>321</v>
@@ -11579,18 +11593,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H312" s="8">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="I312" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11605,13 +11619,13 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G313" s="8">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="H313" s="8">
         <v>17</v>
@@ -11620,7 +11634,7 @@
         <v>310</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11640,7 +11654,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
@@ -11649,18 +11663,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
       <c t="s" r="M314" s="7">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="315" ht="15" customHeight="1">
@@ -11675,13 +11689,13 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>17</v>
@@ -11690,7 +11704,7 @@
         <v>56</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
@@ -11723,7 +11737,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11732,7 +11746,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>309</v>
@@ -11743,7 +11757,7 @@
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
       <c t="s" r="M317" s="7">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="318" ht="14.25" customHeight="1">
@@ -11758,19 +11772,19 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>239</v>
@@ -11778,7 +11792,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -11793,7 +11807,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11805,15 +11819,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -11828,7 +11842,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11876,7 +11890,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F322" s="7">
         <v>320</v>
@@ -11885,18 +11899,18 @@
         <v>60</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
       <c t="s" r="M322" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="323" ht="14.25" customHeight="1">
@@ -11911,27 +11925,27 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -11946,7 +11960,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
@@ -11955,10 +11969,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H324" s="8">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>79</v>
@@ -11981,13 +11995,13 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G325" s="8">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c t="s" r="H325" s="8">
         <v>60</v>
@@ -11996,12 +12010,12 @@
         <v>324</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
       <c t="s" r="M325" s="7">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="326" ht="14.25" customHeight="1">
@@ -12016,7 +12030,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
@@ -12025,13 +12039,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H326" s="8">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12049,22 +12063,22 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G327" s="8">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c t="s" r="H327" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12097,7 +12111,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -12106,10 +12120,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H329" s="8">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c t="s" r="J329" s="7">
         <v>44</v>
@@ -12117,7 +12131,7 @@
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
       <c t="s" r="M329" s="7">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="330" ht="15" customHeight="1">
@@ -12132,13 +12146,13 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>28</v>
@@ -12147,12 +12161,12 @@
         <v>61</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -12167,7 +12181,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12182,7 +12196,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -12200,7 +12214,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -12215,7 +12229,7 @@
         <v>247</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12248,7 +12262,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -12260,15 +12274,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12283,7 +12297,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -12295,7 +12309,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>300</v>
@@ -12303,7 +12317,7 @@
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
       <c t="s" r="M335" s="7">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="336" ht="14.25" customHeight="1">
@@ -12318,7 +12332,7 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
@@ -12336,11 +12350,11 @@
         <v>295</v>
       </c>
       <c t="s" r="K336" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L336" s="7"/>
       <c t="s" r="M336" s="7">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="337" ht="14.25" customHeight="1">
@@ -12355,7 +12369,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12367,7 +12381,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>41</v>
@@ -12377,7 +12391,7 @@
       </c>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12392,7 +12406,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12401,10 +12415,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>225</v>
@@ -12412,7 +12426,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12427,22 +12441,22 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -12460,7 +12474,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
@@ -12469,13 +12483,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12493,22 +12507,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12541,7 +12555,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12550,18 +12564,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="I343" s="7">
         <v>37</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12576,25 +12590,25 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="K344" s="7">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
@@ -12613,7 +12627,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12633,7 +12647,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12648,7 +12662,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12660,15 +12674,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -12683,7 +12697,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12716,7 +12730,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12731,7 +12745,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12764,7 +12778,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F350" s="7">
         <v>321</v>
@@ -12776,7 +12790,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>236</v>
@@ -12784,7 +12798,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -12799,7 +12813,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F351" s="7">
         <v>321</v>
@@ -12808,10 +12822,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H351" s="8">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>256</v>
@@ -12819,7 +12833,7 @@
       <c r="K351" s="7"/>
       <c r="L351" s="7"/>
       <c t="s" r="M351" s="7">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="352" ht="14.25" customHeight="1">
@@ -12834,13 +12848,13 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F352" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G352" s="8">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c t="s" r="H352" s="8">
         <v>60</v>
@@ -12867,7 +12881,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
@@ -12876,10 +12890,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H353" s="8">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>467</v>
+        <v>360</v>
       </c>
       <c t="s" r="J353" s="7">
         <v>297</v>
@@ -12900,13 +12914,13 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G354" s="8">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c t="s" r="H354" s="8">
         <v>60</v>
@@ -12957,10 +12971,10 @@
         <v>234</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>321</v>
@@ -12989,7 +13003,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>76</v>
@@ -12998,7 +13012,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13027,13 +13041,13 @@
         <v>76</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13059,13 +13073,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>29</v>
@@ -13092,16 +13106,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="H360" s="8">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c t="s" r="I360" s="7">
         <v>31</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -13143,10 +13157,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>44</v>
@@ -13154,7 +13168,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13175,7 +13189,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>60</v>
@@ -13184,7 +13198,7 @@
         <v>61</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13213,13 +13227,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H364" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="I364" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -13243,13 +13257,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G365" s="8">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="H365" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>82</v>
@@ -13279,7 +13293,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c t="s" r="I366" s="7">
         <v>283</v>
@@ -13309,7 +13323,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c t="s" r="H367" s="8">
         <v>60</v>
@@ -13366,7 +13380,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13398,10 +13412,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13430,10 +13444,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c t="s" r="I371" s="7">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c t="s" r="J371" s="7">
         <v>324</v>
@@ -13462,7 +13476,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>60</v>
@@ -13534,7 +13548,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>482</v>
@@ -13585,12 +13599,12 @@
         <v>67</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
       <c t="s" r="M376" s="7">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="377" ht="14.25" customHeight="1">
@@ -13620,7 +13634,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13655,7 +13669,7 @@
         <v>229</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13687,7 +13701,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c t="s" r="J379" s="7">
         <v>25</v>
@@ -13695,7 +13709,7 @@
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -13722,10 +13736,10 @@
         <v>238</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13755,10 +13769,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>233</v>
+        <v>359</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13800,10 +13814,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H383" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c t="s" r="J383" s="7">
         <v>42</v>
@@ -13811,7 +13825,7 @@
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
       <c t="s" r="M383" s="7">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="384" ht="14.25" customHeight="1">
@@ -13832,7 +13846,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G384" s="8">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c t="s" r="H384" s="8">
         <v>60</v>
@@ -13876,7 +13890,7 @@
         <v>297</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13921,7 +13935,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J387" s="7">
         <v>236</v>
@@ -13929,7 +13943,7 @@
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14026,7 +14040,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c t="s" r="J390" s="7">
         <v>225</v>
@@ -14092,7 +14106,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c t="s" r="J392" s="7">
         <v>319</v>
@@ -14140,7 +14154,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>300</v>
@@ -14172,7 +14186,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="I395" s="7">
         <v>287</v>
@@ -14204,16 +14218,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>262</v>
+        <v>224</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14244,7 +14258,7 @@
         <v>5805</v>
       </c>
       <c t="s" r="C398" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
@@ -14260,7 +14274,7 @@
         <v>492</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>54</v>
@@ -14268,7 +14282,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14279,7 +14293,7 @@
         <v>5806</v>
       </c>
       <c t="s" r="C399" s="7">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
@@ -14295,10 +14309,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -14346,7 +14360,7 @@
         <v>259</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -14429,7 +14443,7 @@
         <v>310</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>325</v>
+        <v>423</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
@@ -14461,7 +14475,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>232</v>
+        <v>281</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>47</v>
@@ -14494,10 +14508,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c t="s" r="J406" s="7">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
@@ -14545,7 +14559,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14577,10 +14591,10 @@
         <v>502</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14615,7 +14629,7 @@
         <v>475</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -14668,7 +14682,7 @@
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -14695,7 +14709,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>44</v>
@@ -14765,7 +14779,7 @@
         <v>505</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>506</v>
@@ -14798,7 +14812,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I416" s="7">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c t="s" r="J416" s="7">
         <v>507</v>
@@ -14846,10 +14860,10 @@
         <v>509</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14881,10 +14895,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c t="s" r="J419" s="7">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K419" s="7"/>
       <c r="L419" s="7"/>

--- a/Data/FlightPlan/FPL_16OCT26.xlsx
+++ b/Data/FlightPlan/FPL_16OCT26.xlsx
@@ -509,6 +509,9 @@
     <t>00:55</t>
   </si>
   <si>
+    <t>00:53</t>
+  </si>
+  <si>
     <t>VN-A532</t>
   </si>
   <si>
@@ -953,6 +956,9 @@
     <t>22:35</t>
   </si>
   <si>
+    <t>23:47</t>
+  </si>
+  <si>
     <t>VN-A580</t>
   </si>
   <si>
@@ -980,6 +986,9 @@
     <t>22:30</t>
   </si>
   <si>
+    <t>23:46</t>
+  </si>
+  <si>
     <t>VN-A607</t>
   </si>
   <si>
@@ -1064,6 +1073,9 @@
     <t>15:09</t>
   </si>
   <si>
+    <t>05:38</t>
+  </si>
+  <si>
     <t>VN-A634</t>
   </si>
   <si>
@@ -1232,6 +1244,9 @@
     <t>CAN</t>
   </si>
   <si>
+    <t>01:18</t>
+  </si>
+  <si>
     <t>02:10</t>
   </si>
   <si>
@@ -1442,9 +1457,6 @@
     <t>19:14</t>
   </si>
   <si>
-    <t>01:18</t>
-  </si>
-  <si>
     <t>02:20</t>
   </si>
   <si>
@@ -1670,6 +1682,9 @@
     <t>01:30</t>
   </si>
   <si>
+    <t>02:01</t>
+  </si>
+  <si>
     <t>04:10</t>
   </si>
   <si>
@@ -1802,7 +1817,7 @@
     <t>Total Record(s): 341</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 16, 2026 22:08</t>
+    <t xml:space="preserve">Generated on  Oct 16, 2026 23:01</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -4194,7 +4209,9 @@
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
-      <c r="M65" s="7"/>
+      <c t="s" r="M65" s="7">
+        <v>166</v>
+      </c>
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c r="A66" s="6"/>
@@ -4223,7 +4240,7 @@
       </c>
       <c r="D67" s="7"/>
       <c t="s" r="E67" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F67" s="7">
         <v>321</v>
@@ -4232,10 +4249,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H67" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I67" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="J67" s="7">
         <v>149</v>
@@ -4243,7 +4260,7 @@
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c t="s" r="M67" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="68" ht="14.25" customHeight="1">
@@ -4258,13 +4275,13 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G68" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H68" s="8">
         <v>62</v>
@@ -4278,7 +4295,7 @@
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4293,7 +4310,7 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
@@ -4313,7 +4330,7 @@
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4328,7 +4345,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4340,7 +4357,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J70" s="7">
         <v>45</v>
@@ -4348,7 +4365,7 @@
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4363,7 +4380,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4375,7 +4392,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>85</v>
@@ -4383,7 +4400,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4398,7 +4415,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4413,12 +4430,12 @@
         <v>33</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
       <c t="s" r="M72" s="7">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="73" ht="14.25" customHeight="1">
@@ -4433,7 +4450,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4445,7 +4462,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I73" s="7">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c t="s" r="J73" s="7">
         <v>128</v>
@@ -4481,7 +4498,7 @@
       </c>
       <c r="D75" s="7"/>
       <c t="s" r="E75" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F75" s="7">
         <v>321</v>
@@ -4493,15 +4510,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I75" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J75" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c t="s" r="M75" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="76" ht="14.25" customHeight="1">
@@ -4516,7 +4533,7 @@
       </c>
       <c r="D76" s="7"/>
       <c t="s" r="E76" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F76" s="7">
         <v>321</v>
@@ -4536,7 +4553,7 @@
       <c r="K76" s="7"/>
       <c r="L76" s="7"/>
       <c t="s" r="M76" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
@@ -4551,7 +4568,7 @@
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
@@ -4563,15 +4580,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K77" s="7"/>
       <c r="L77" s="7"/>
       <c t="s" r="M77" s="7">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
@@ -4586,7 +4603,7 @@
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
@@ -4598,15 +4615,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I78" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
       <c t="s" r="M78" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="79" ht="14.25" customHeight="1">
@@ -4621,7 +4638,7 @@
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
@@ -4630,7 +4647,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>156</v>
@@ -4641,7 +4658,7 @@
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
       <c t="s" r="M79" s="7">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="80" ht="15" customHeight="1">
@@ -4656,13 +4673,13 @@
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H80" s="8">
         <v>28</v>
@@ -4676,7 +4693,7 @@
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c t="s" r="M80" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
@@ -4691,7 +4708,7 @@
       </c>
       <c r="D81" s="7"/>
       <c t="s" r="E81" s="7">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F81" s="7">
         <v>321</v>
@@ -4703,17 +4720,17 @@
         <v>62</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c t="s" r="K81" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L81" s="7"/>
       <c t="s" r="M81" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" ht="14.25" customHeight="1">
@@ -4743,7 +4760,7 @@
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4755,17 +4772,17 @@
         <v>91</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>81</v>
       </c>
       <c t="s" r="K83" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4780,7 +4797,7 @@
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
@@ -4795,14 +4812,14 @@
         <v>84</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c t="s" r="K84" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="L84" s="7"/>
       <c t="s" r="M84" s="7">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="85" ht="15" customHeight="1">
@@ -4817,7 +4834,7 @@
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
@@ -4826,18 +4843,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4852,22 +4869,22 @@
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4900,7 +4917,7 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
@@ -4912,10 +4929,10 @@
         <v>113</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4935,7 +4952,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4947,7 +4964,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J89" s="7">
         <v>45</v>
@@ -4955,7 +4972,7 @@
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
       <c t="s" r="M89" s="7">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -4970,7 +4987,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4979,20 +4996,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J90" s="7">
         <v>25</v>
       </c>
       <c t="s" r="K90" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -5007,13 +5024,13 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>28</v>
@@ -5022,14 +5039,14 @@
         <v>119</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c t="s" r="K91" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="L91" s="7"/>
       <c t="s" r="M91" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" ht="14.25" customHeight="1">
@@ -5044,7 +5061,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -5056,10 +5073,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -5092,7 +5109,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -5104,15 +5121,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -5127,7 +5144,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -5139,7 +5156,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c t="s" r="J95" s="7">
         <v>45</v>
@@ -5147,7 +5164,7 @@
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
       <c t="s" r="M95" s="7">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" ht="14.25" customHeight="1">
@@ -5162,7 +5179,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -5174,15 +5191,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J96" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
       <c t="s" r="M96" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="97" ht="14.25" customHeight="1">
@@ -5197,7 +5214,7 @@
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
@@ -5209,15 +5226,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c t="s" r="M97" s="7">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="98" ht="14.25" customHeight="1">
@@ -5232,7 +5249,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -5244,15 +5261,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -5267,7 +5284,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -5276,7 +5293,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I99" s="7">
         <v>51</v>
@@ -5315,7 +5332,7 @@
       </c>
       <c r="D101" s="7"/>
       <c t="s" r="E101" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F101" s="7">
         <v>321</v>
@@ -5335,7 +5352,7 @@
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c t="s" r="M101" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="102" ht="14.25" customHeight="1">
@@ -5350,7 +5367,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -5362,7 +5379,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J102" s="7">
         <v>22</v>
@@ -5370,7 +5387,7 @@
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -5385,7 +5402,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -5400,7 +5417,7 @@
         <v>145</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -5420,7 +5437,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -5435,12 +5452,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
       <c t="s" r="M104" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="105" ht="15" customHeight="1">
@@ -5455,7 +5472,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -5467,13 +5484,13 @@
         <v>127</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="K105" s="7">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L105" s="7"/>
       <c t="s" r="M105" s="7">
@@ -5492,7 +5509,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5504,17 +5521,17 @@
         <v>62</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="K106" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L106" s="7"/>
       <c t="s" r="M106" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" ht="14.25" customHeight="1">
@@ -5544,7 +5561,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5553,10 +5570,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H108" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>22</v>
@@ -5564,7 +5581,7 @@
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
       <c t="s" r="M108" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" ht="14.25" customHeight="1">
@@ -5579,13 +5596,13 @@
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G109" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H109" s="8">
         <v>28</v>
@@ -5599,7 +5616,7 @@
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c t="s" r="M109" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="110" ht="15" customHeight="1">
@@ -5614,7 +5631,7 @@
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5626,15 +5643,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5649,7 +5666,7 @@
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5658,20 +5675,20 @@
         <v>62</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="K111" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L111" s="7"/>
       <c t="s" r="M111" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="112" ht="14.25" customHeight="1">
@@ -5686,29 +5703,29 @@
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="H112" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="K112" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L112" s="7"/>
       <c t="s" r="M112" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="113" ht="14.25" customHeight="1">
@@ -5738,7 +5755,7 @@
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
@@ -5747,18 +5764,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
       <c t="s" r="M114" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
@@ -5773,27 +5790,27 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G115" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H115" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5808,7 +5825,7 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
@@ -5817,7 +5834,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I116" s="7">
         <v>82</v>
@@ -5828,7 +5845,7 @@
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5843,27 +5860,27 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H117" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5878,7 +5895,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5887,18 +5904,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
       <c t="s" r="M118" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="119" ht="14.25" customHeight="1">
@@ -5913,27 +5930,27 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H119" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c t="s" r="M119" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="120" ht="15" customHeight="1">
@@ -5963,7 +5980,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5975,10 +5992,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5998,7 +6015,7 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
@@ -6010,7 +6027,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>56</v>
@@ -6018,7 +6035,7 @@
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
       <c t="s" r="M122" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
@@ -6048,13 +6065,13 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>62</v>
@@ -6068,7 +6085,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -6083,7 +6100,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -6095,17 +6112,17 @@
         <v>113</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="K125" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L125" s="7"/>
       <c t="s" r="M125" s="7">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="126" ht="14.25" customHeight="1">
@@ -6120,7 +6137,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -6129,18 +6146,18 @@
         <v>113</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I126" s="7">
         <v>157</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
       <c t="s" r="M126" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="127" ht="14.25" customHeight="1">
@@ -6170,7 +6187,7 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -6182,10 +6199,10 @@
         <v>75</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -6205,7 +6222,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -6240,7 +6257,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -6252,7 +6269,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>72</v>
@@ -6260,7 +6277,7 @@
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
       <c t="s" r="M130" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="131" ht="14.25" customHeight="1">
@@ -6290,7 +6307,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -6299,10 +6316,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>134</v>
@@ -6325,22 +6342,22 @@
       </c>
       <c r="D133" s="7"/>
       <c t="s" r="E133" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F133" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H133" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I133" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J133" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
@@ -6360,7 +6377,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -6372,7 +6389,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>104</v>
@@ -6380,7 +6397,7 @@
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -6395,7 +6412,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -6410,12 +6427,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -6430,7 +6447,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -6442,14 +6459,16 @@
         <v>28</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
-      <c r="M136" s="7"/>
+      <c t="s" r="M136" s="7">
+        <v>37</v>
+      </c>
     </row>
     <row r="137" ht="14.25" customHeight="1">
       <c r="A137" s="6"/>
@@ -6478,13 +6497,13 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="H138" s="8">
         <v>28</v>
@@ -6493,12 +6512,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c t="s" r="M138" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="139" ht="14.25" customHeight="1">
@@ -6513,7 +6532,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6525,15 +6544,15 @@
         <v>75</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c t="s" r="M139" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="140" ht="15" customHeight="1">
@@ -6563,7 +6582,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6578,12 +6597,12 @@
         <v>130</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6598,7 +6617,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -6610,17 +6629,17 @@
         <v>62</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c t="s" r="K142" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6635,7 +6654,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6653,11 +6672,11 @@
         <v>138</v>
       </c>
       <c t="s" r="K143" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L143" s="7"/>
       <c t="s" r="M143" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="144" ht="14.25" customHeight="1">
@@ -6672,7 +6691,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6684,17 +6703,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>161</v>
       </c>
       <c t="s" r="K144" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L144" s="7"/>
       <c t="s" r="M144" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
@@ -6709,7 +6728,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -6721,17 +6740,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="K145" s="7">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="L145" s="7"/>
       <c t="s" r="M145" s="7">
-        <v>34</v>
+        <v>315</v>
       </c>
     </row>
     <row r="146" ht="14.25" customHeight="1">
@@ -6761,7 +6780,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6781,7 +6800,7 @@
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
       <c t="s" r="M147" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="148" ht="14.25" customHeight="1">
@@ -6796,7 +6815,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6808,7 +6827,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J148" s="7">
         <v>58</v>
@@ -6816,7 +6835,7 @@
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
       <c t="s" r="M148" s="7">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="149" ht="14.25" customHeight="1">
@@ -6831,7 +6850,7 @@
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
@@ -6843,15 +6862,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I149" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c t="s" r="J149" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
       <c t="s" r="M149" s="7">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
@@ -6866,7 +6885,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6881,12 +6900,12 @@
         <v>85</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6901,7 +6920,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6916,14 +6935,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="K151" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>87</v>
+        <v>325</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6953,27 +6972,27 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
       <c t="s" r="M153" s="7">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="154" ht="14.25" customHeight="1">
@@ -6988,7 +7007,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6997,7 +7016,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c t="s" r="I154" s="7">
         <v>65</v>
@@ -7036,7 +7055,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -7048,10 +7067,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -7071,7 +7090,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -7080,10 +7099,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H157" s="8">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J157" s="7">
         <v>80</v>
@@ -7091,7 +7110,7 @@
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -7106,27 +7125,27 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G158" s="8">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c t="s" r="H158" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -7141,7 +7160,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -7161,7 +7180,7 @@
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c t="s" r="M159" s="7">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="160" ht="15" customHeight="1">
@@ -7176,7 +7195,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -7196,7 +7215,7 @@
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c t="s" r="M160" s="7">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="161" ht="14.25" customHeight="1">
@@ -7211,7 +7230,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -7223,7 +7242,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c t="s" r="J161" s="7">
         <v>48</v>
@@ -7231,7 +7250,7 @@
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c t="s" r="M161" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="162" ht="14.25" customHeight="1">
@@ -7246,7 +7265,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -7261,12 +7280,12 @@
         <v>88</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -7296,7 +7315,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7331,7 +7350,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -7343,15 +7362,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
       <c t="s" r="M165" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="166" ht="14.25" customHeight="1">
@@ -7381,7 +7400,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7393,15 +7412,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7416,7 +7435,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -7428,15 +7447,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7451,7 +7470,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -7463,7 +7482,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>101</v>
@@ -7473,7 +7492,7 @@
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -7488,7 +7507,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -7506,11 +7525,11 @@
         <v>27</v>
       </c>
       <c t="s" r="K170" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L170" s="7"/>
       <c t="s" r="M170" s="7">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="171" ht="14.25" customHeight="1">
@@ -7525,7 +7544,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -7534,20 +7553,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>94</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c t="s" r="K171" s="7">
         <v>157</v>
       </c>
       <c r="L171" s="7"/>
       <c t="s" r="M171" s="7">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="172" ht="14.25" customHeight="1">
@@ -7562,13 +7581,13 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H172" s="8">
         <v>28</v>
@@ -7577,14 +7596,14 @@
         <v>106</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="K172" s="7">
         <v>33</v>
       </c>
       <c r="L172" s="7"/>
       <c t="s" r="M172" s="7">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="173" ht="14.25" customHeight="1">
@@ -7614,7 +7633,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7629,12 +7648,12 @@
         <v>144</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7649,7 +7668,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7661,7 +7680,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>135</v>
@@ -7669,7 +7688,7 @@
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7684,7 +7703,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7693,17 +7712,19 @@
         <v>75</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c r="M176" s="7"/>
+      <c t="s" r="M176" s="7">
+        <v>354</v>
+      </c>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c r="A177" s="6"/>
@@ -7732,7 +7753,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7744,15 +7765,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
       <c t="s" r="M178" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="179" ht="14.25" customHeight="1">
@@ -7767,7 +7788,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -7779,15 +7800,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
       <c t="s" r="M179" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="180" ht="15" customHeight="1">
@@ -7802,7 +7823,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7814,15 +7835,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7837,7 +7858,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7872,7 +7893,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7890,11 +7911,11 @@
         <v>102</v>
       </c>
       <c t="s" r="K182" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7909,7 +7930,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7921,7 +7942,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>47</v>
@@ -7929,7 +7950,7 @@
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c t="s" r="M183" s="7">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="184" ht="14.25" customHeight="1">
@@ -7959,7 +7980,7 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
@@ -7968,10 +7989,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H185" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>82</v>
@@ -7979,7 +8000,7 @@
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
       <c t="s" r="M185" s="7">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
@@ -7994,19 +8015,19 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="H186" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c t="s" r="J186" s="7">
         <v>58</v>
@@ -8029,7 +8050,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -8044,12 +8065,12 @@
         <v>159</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -8064,7 +8085,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -8076,15 +8097,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -8114,7 +8135,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -8134,7 +8155,7 @@
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
       <c t="s" r="M190" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="191" ht="14.25" customHeight="1">
@@ -8149,7 +8170,7 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
@@ -8161,15 +8182,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
       <c t="s" r="M191" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="192" ht="14.25" customHeight="1">
@@ -8184,7 +8205,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -8193,10 +8214,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c t="s" r="J192" s="7">
         <v>65</v>
@@ -8219,22 +8240,22 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="H193" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -8267,7 +8288,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -8276,18 +8297,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>376</v>
+        <v>380</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8302,27 +8323,27 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c t="s" r="M196" s="7">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="197" ht="14.25" customHeight="1">
@@ -8337,27 +8358,27 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H197" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c t="s" r="M197" s="7">
-        <v>379</v>
+        <v>383</v>
       </c>
     </row>
     <row r="198" ht="14.25" customHeight="1">
@@ -8372,19 +8393,19 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>145</v>
@@ -8392,7 +8413,7 @@
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c t="s" r="M198" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="199" ht="14.25" customHeight="1">
@@ -8407,7 +8428,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -8416,10 +8437,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H199" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>156</v>
@@ -8427,7 +8448,7 @@
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c t="s" r="M199" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="200" ht="15" customHeight="1">
@@ -8442,27 +8463,27 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H200" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
       <c t="s" r="M200" s="7">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="201" ht="14.25" customHeight="1">
@@ -8477,7 +8498,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -8489,7 +8510,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>140</v>
@@ -8497,7 +8518,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8527,7 +8548,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8539,15 +8560,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
       <c t="s" r="M203" s="7">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="204" ht="14.25" customHeight="1">
@@ -8562,7 +8583,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8574,7 +8595,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c t="s" r="J204" s="7">
         <v>80</v>
@@ -8582,7 +8603,7 @@
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
       <c t="s" r="M204" s="7">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
@@ -8597,7 +8618,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8609,15 +8630,15 @@
         <v>113</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
       <c t="s" r="M205" s="7">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="206" ht="14.25" customHeight="1">
@@ -8632,7 +8653,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8654,7 +8675,7 @@
       </c>
       <c r="L206" s="7"/>
       <c t="s" r="M206" s="7">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="207" ht="14.25" customHeight="1">
@@ -8669,7 +8690,7 @@
       </c>
       <c r="D207" s="7"/>
       <c t="s" r="E207" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F207" s="7">
         <v>321</v>
@@ -8691,7 +8712,7 @@
       </c>
       <c r="L207" s="7"/>
       <c t="s" r="M207" s="7">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="208" ht="14.25" customHeight="1">
@@ -8706,7 +8727,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8718,7 +8739,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>85</v>
@@ -8728,7 +8749,7 @@
       </c>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8758,13 +8779,13 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H210" s="8">
         <v>75</v>
@@ -8773,12 +8794,12 @@
         <v>149</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8793,7 +8814,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8808,12 +8829,12 @@
         <v>119</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
       <c t="s" r="M211" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="212" ht="14.25" customHeight="1">
@@ -8828,7 +8849,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8840,17 +8861,17 @@
         <v>100</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c t="s" r="K212" s="7">
         <v>47</v>
       </c>
       <c r="L212" s="7"/>
       <c t="s" r="M212" s="7">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="213" ht="14.25" customHeight="1">
@@ -8865,7 +8886,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8877,17 +8898,17 @@
         <v>62</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c t="s" r="K213" s="7">
         <v>59</v>
       </c>
       <c r="L213" s="7"/>
       <c t="s" r="M213" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="214" ht="14.25" customHeight="1">
@@ -8902,7 +8923,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8914,14 +8935,18 @@
         <v>16</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>396</v>
-      </c>
-      <c r="K214" s="7"/>
+        <v>400</v>
+      </c>
+      <c t="s" r="K214" s="7">
+        <v>65</v>
+      </c>
       <c r="L214" s="7"/>
-      <c r="M214" s="7"/>
+      <c t="s" r="M214" s="7">
+        <v>55</v>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
       <c r="A215" s="6"/>
@@ -8950,7 +8975,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8962,7 +8987,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c t="s" r="J216" s="7">
         <v>38</v>
@@ -8970,7 +8995,7 @@
       <c r="K216" s="7"/>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8985,7 +9010,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8997,17 +9022,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c t="s" r="K217" s="7">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -9022,7 +9047,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -9037,14 +9062,14 @@
         <v>41</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c t="s" r="K218" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="L218" s="7"/>
       <c t="s" r="M218" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="219" ht="14.25" customHeight="1">
@@ -9059,7 +9084,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -9071,7 +9096,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J219" s="7">
         <v>43</v>
@@ -9081,7 +9106,7 @@
       </c>
       <c r="L219" s="7"/>
       <c t="s" r="M219" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="220" ht="15" customHeight="1">
@@ -9096,7 +9121,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -9108,7 +9133,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>84</v>
@@ -9118,7 +9143,7 @@
       </c>
       <c r="L220" s="7"/>
       <c t="s" r="M220" s="7">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="221" ht="14.25" customHeight="1">
@@ -9133,7 +9158,7 @@
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -9142,7 +9167,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="I221" s="7">
         <v>119</v>
@@ -9168,27 +9193,27 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G222" s="8">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="H222" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -9203,7 +9228,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -9212,17 +9237,19 @@
         <v>28</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
-      <c r="M223" s="7"/>
+      <c t="s" r="M223" s="7">
+        <v>411</v>
+      </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
       <c t="s" r="A224" s="6">
@@ -9236,22 +9263,22 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="H224" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -9284,7 +9311,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -9293,18 +9320,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
       <c t="s" r="M226" s="7">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="227" ht="14.25" customHeight="1">
@@ -9319,13 +9346,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>62</v>
@@ -9334,12 +9361,12 @@
         <v>41</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
       <c t="s" r="M227" s="7">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="228" ht="14.25" customHeight="1">
@@ -9354,7 +9381,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9363,10 +9390,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J228" s="7">
         <v>25</v>
@@ -9374,7 +9401,7 @@
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
       <c t="s" r="M228" s="7">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="229" ht="14.25" customHeight="1">
@@ -9389,13 +9416,13 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>62</v>
@@ -9404,12 +9431,12 @@
         <v>119</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
       <c t="s" r="M229" s="7">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="230" ht="15" customHeight="1">
@@ -9439,13 +9466,13 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="H231" s="8">
         <v>28</v>
@@ -9454,12 +9481,12 @@
         <v>150</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9474,7 +9501,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9483,10 +9510,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>47</v>
@@ -9494,7 +9521,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9509,13 +9536,13 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c t="s" r="H233" s="8">
         <v>28</v>
@@ -9524,12 +9551,12 @@
         <v>72</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c t="s" r="M233" s="7">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="234" ht="14.25" customHeight="1">
@@ -9544,7 +9571,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -9556,7 +9583,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>38</v>
@@ -9592,7 +9619,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -9601,18 +9628,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H236" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I236" s="7">
         <v>82</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c t="s" r="M236" s="7">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="237" ht="14.25" customHeight="1">
@@ -9627,13 +9654,13 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H237" s="8">
         <v>17</v>
@@ -9642,12 +9669,12 @@
         <v>25</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
       <c t="s" r="M237" s="7">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="238" ht="14.25" customHeight="1">
@@ -9662,7 +9689,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9674,15 +9701,15 @@
         <v>21</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9697,7 +9724,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9709,7 +9736,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I239" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c t="s" r="J239" s="7">
         <v>140</v>
@@ -9717,7 +9744,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9732,7 +9759,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -9741,13 +9768,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9780,7 +9807,7 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
@@ -9800,7 +9827,7 @@
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
       <c t="s" r="M242" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="243" ht="14.25" customHeight="1">
@@ -9815,7 +9842,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9824,18 +9851,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9850,13 +9877,13 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>62</v>
@@ -9865,12 +9892,12 @@
         <v>48</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c t="s" r="M244" s="7">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="245" ht="15" customHeight="1">
@@ -9885,7 +9912,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9897,7 +9924,7 @@
         <v>54</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>55</v>
@@ -9933,7 +9960,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9968,7 +9995,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9990,7 +10017,7 @@
       </c>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -10005,7 +10032,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -10023,11 +10050,11 @@
         <v>59</v>
       </c>
       <c t="s" r="K249" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -10042,7 +10069,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -10051,13 +10078,13 @@
         <v>28</v>
       </c>
       <c t="s" r="H250" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c t="s" r="J250" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
@@ -10090,19 +10117,19 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H252" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c t="s" r="J252" s="7">
         <v>81</v>
@@ -10110,7 +10137,7 @@
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c t="s" r="M252" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="253" ht="14.25" customHeight="1">
@@ -10125,7 +10152,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -10134,18 +10161,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H253" s="8">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c t="s" r="I253" s="7">
         <v>84</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -10160,19 +10187,19 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G254" s="8">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c t="s" r="H254" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>88</v>
@@ -10180,7 +10207,7 @@
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -10210,7 +10237,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -10222,7 +10249,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>45</v>
@@ -10230,7 +10257,7 @@
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c t="s" r="M256" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="257" ht="14.25" customHeight="1">
@@ -10245,7 +10272,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -10260,12 +10287,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
       <c t="s" r="M257" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="258" ht="14.25" customHeight="1">
@@ -10280,7 +10307,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -10289,7 +10316,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I258" s="7">
         <v>29</v>
@@ -10300,7 +10327,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -10315,27 +10342,27 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H259" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c t="s" r="M259" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="260" ht="15" customHeight="1">
@@ -10350,7 +10377,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -10365,14 +10392,14 @@
         <v>59</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c t="s" r="K260" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L260" s="7"/>
       <c t="s" r="M260" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
@@ -10387,7 +10414,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -10399,10 +10426,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c t="s" r="J261" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c t="s" r="K261" s="7">
         <v>87</v>
@@ -10424,7 +10451,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -10433,13 +10460,13 @@
         <v>62</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -10472,7 +10499,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F264" s="7">
         <v>320</v>
@@ -10481,10 +10508,10 @@
         <v>62</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c t="s" r="J264" s="7">
         <v>128</v>
@@ -10492,7 +10519,7 @@
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -10507,13 +10534,13 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F265" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G265" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="H265" s="8">
         <v>62</v>
@@ -10527,7 +10554,7 @@
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c t="s" r="M265" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="266" ht="14.25" customHeight="1">
@@ -10542,7 +10569,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F266" s="7">
         <v>320</v>
@@ -10551,18 +10578,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H266" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c t="s" r="M266" s="7">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="267" ht="14.25" customHeight="1">
@@ -10577,27 +10604,27 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F267" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H267" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c t="s" r="M267" s="7">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="268" ht="14.25" customHeight="1">
@@ -10612,7 +10639,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F268" s="7">
         <v>320</v>
@@ -10621,7 +10648,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H268" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="I268" s="7">
         <v>104</v>
@@ -10632,7 +10659,7 @@
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c t="s" r="M268" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="269" ht="14.25" customHeight="1">
@@ -10647,19 +10674,19 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F269" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="H269" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c t="s" r="J269" s="7">
         <v>95</v>
@@ -10667,7 +10694,7 @@
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
       <c t="s" r="M269" s="7">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="270" ht="15" customHeight="1">
@@ -10682,7 +10709,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="F270" s="7">
         <v>320</v>
@@ -10694,17 +10721,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="K270" s="7">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10734,7 +10761,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10743,18 +10770,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
       <c t="s" r="M272" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="273" ht="14.25" customHeight="1">
@@ -10769,19 +10796,19 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c t="s" r="J273" s="7">
         <v>145</v>
@@ -10789,7 +10816,7 @@
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
       <c t="s" r="M273" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="274" ht="14.25" customHeight="1">
@@ -10804,7 +10831,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -10813,7 +10840,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>84</v>
@@ -10824,7 +10851,7 @@
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
       <c t="s" r="M274" s="7">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="275" ht="15" customHeight="1">
@@ -10839,27 +10866,27 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10874,7 +10901,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -10883,20 +10910,20 @@
         <v>62</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>85</v>
       </c>
       <c t="s" r="K276" s="7">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="L276" s="7"/>
       <c t="s" r="M276" s="7">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="277" ht="14.25" customHeight="1">
@@ -10911,13 +10938,13 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G277" s="8">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c t="s" r="H277" s="8">
         <v>62</v>
@@ -10926,14 +10953,14 @@
         <v>48</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c t="s" r="K277" s="7">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="L277" s="7"/>
       <c t="s" r="M277" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="278" ht="14.25" customHeight="1">
@@ -10963,7 +10990,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
@@ -10972,7 +10999,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c t="s" r="I279" s="7">
         <v>58</v>
@@ -10983,7 +11010,7 @@
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10998,22 +11025,22 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -11046,7 +11073,7 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
@@ -11058,15 +11085,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
       <c t="s" r="M282" s="7">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="283" ht="14.25" customHeight="1">
@@ -11081,7 +11108,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F283" s="7">
         <v>320</v>
@@ -11101,7 +11128,7 @@
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
       <c t="s" r="M283" s="7">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="284" ht="14.25" customHeight="1">
@@ -11116,7 +11143,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F284" s="7">
         <v>320</v>
@@ -11131,12 +11158,12 @@
         <v>145</v>
       </c>
       <c t="s" r="J284" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -11151,7 +11178,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F285" s="7">
         <v>320</v>
@@ -11160,18 +11187,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -11186,19 +11213,19 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F286" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H286" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>138</v>
@@ -11206,7 +11233,7 @@
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
       <c t="s" r="M286" s="7">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="287" ht="14.25" customHeight="1">
@@ -11221,7 +11248,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F287" s="7">
         <v>320</v>
@@ -11230,10 +11257,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>124</v>
@@ -11241,7 +11268,7 @@
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
       <c t="s" r="M287" s="7">
-        <v>477</v>
+        <v>411</v>
       </c>
     </row>
     <row r="288" ht="14.25" customHeight="1">
@@ -11256,22 +11283,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="F288" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -11304,7 +11331,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -11319,12 +11346,12 @@
         <v>98</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -11339,7 +11366,7 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F291" s="7">
         <v>321</v>
@@ -11351,15 +11378,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
       <c t="s" r="M291" s="7">
-        <v>481</v>
+        <v>485</v>
       </c>
     </row>
     <row r="292" ht="14.25" customHeight="1">
@@ -11374,7 +11401,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -11389,14 +11416,14 @@
         <v>152</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c t="s" r="K292" s="7">
         <v>133</v>
       </c>
       <c r="L292" s="7"/>
       <c t="s" r="M292" s="7">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="293" ht="14.25" customHeight="1">
@@ -11411,7 +11438,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -11423,17 +11450,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c t="s" r="K293" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="L293" s="7"/>
       <c t="s" r="M293" s="7">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="294" ht="14.25" customHeight="1">
@@ -11448,7 +11475,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -11463,14 +11490,14 @@
         <v>27</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="K294" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -11485,7 +11512,7 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
@@ -11500,14 +11527,14 @@
         <v>85</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c t="s" r="K295" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="L295" s="7"/>
       <c t="s" r="M295" s="7">
-        <v>486</v>
+        <v>490</v>
       </c>
     </row>
     <row r="296" ht="14.25" customHeight="1">
@@ -11537,7 +11564,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F297" s="7">
         <v>320</v>
@@ -11546,7 +11573,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I297" s="7">
         <v>92</v>
@@ -11557,7 +11584,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11572,13 +11599,13 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F298" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>28</v>
@@ -11587,12 +11614,12 @@
         <v>134</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
       <c t="s" r="M298" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
@@ -11607,7 +11634,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F299" s="7">
         <v>320</v>
@@ -11616,18 +11643,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>156</v>
       </c>
       <c t="s" r="J299" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K299" s="7"/>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
-        <v>491</v>
+        <v>495</v>
       </c>
     </row>
     <row r="300" ht="15" customHeight="1">
@@ -11642,13 +11669,13 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F300" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>28</v>
@@ -11657,12 +11684,12 @@
         <v>157</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11692,7 +11719,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -11701,18 +11728,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="I302" s="7">
         <v>130</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
       <c t="s" r="M302" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="303" ht="14.25" customHeight="1">
@@ -11727,13 +11754,13 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>62</v>
@@ -11742,12 +11769,12 @@
         <v>81</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
       <c t="s" r="M303" s="7">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="304" ht="14.25" customHeight="1">
@@ -11762,7 +11789,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -11771,18 +11798,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>119</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11797,27 +11824,27 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
       <c t="s" r="M305" s="7">
-        <v>498</v>
+        <v>502</v>
       </c>
     </row>
     <row r="306" ht="14.25" customHeight="1">
@@ -11847,7 +11874,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11859,10 +11886,10 @@
         <v>62</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11882,7 +11909,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11894,15 +11921,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
       <c t="s" r="M308" s="7">
-        <v>501</v>
+        <v>505</v>
       </c>
     </row>
     <row r="309" ht="14.25" customHeight="1">
@@ -11917,7 +11944,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
@@ -11937,7 +11964,7 @@
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
       <c t="s" r="M309" s="7">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="310" ht="15" customHeight="1">
@@ -11952,7 +11979,7 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F310" s="7">
         <v>320</v>
@@ -11964,15 +11991,15 @@
         <v>100</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
       <c t="s" r="M310" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="311" ht="14.25" customHeight="1">
@@ -11987,7 +12014,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -12007,7 +12034,7 @@
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -12037,7 +12064,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F313" s="7">
         <v>321</v>
@@ -12046,18 +12073,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="I313" s="7">
         <v>38</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>505</v>
+        <v>509</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -12072,22 +12099,22 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F314" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -12107,7 +12134,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F315" s="7">
         <v>321</v>
@@ -12127,7 +12154,7 @@
       <c r="K315" s="7"/>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="316" ht="14.25" customHeight="1">
@@ -12142,7 +12169,7 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F316" s="7">
         <v>321</v>
@@ -12157,12 +12184,12 @@
         <v>58</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="317" ht="14.25" customHeight="1">
@@ -12192,7 +12219,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -12204,7 +12231,7 @@
         <v>113</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>19</v>
@@ -12212,7 +12239,7 @@
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
       <c t="s" r="M318" s="7">
-        <v>509</v>
+        <v>513</v>
       </c>
     </row>
     <row r="319" ht="14.25" customHeight="1">
@@ -12227,7 +12254,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -12239,15 +12266,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I319" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="J319" s="7">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K319" s="7"/>
       <c r="L319" s="7"/>
       <c t="s" r="M319" s="7">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="320" ht="15" customHeight="1">
@@ -12262,7 +12289,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -12274,15 +12301,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -12297,7 +12324,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F321" s="7">
         <v>320</v>
@@ -12309,7 +12336,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>29</v>
@@ -12347,7 +12374,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F323" s="7">
         <v>320</v>
@@ -12356,18 +12383,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
       <c t="s" r="M323" s="7">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="324" ht="14.25" customHeight="1">
@@ -12382,27 +12409,27 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F324" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
       <c t="s" r="M324" s="7">
-        <v>515</v>
+        <v>519</v>
       </c>
     </row>
     <row r="325" ht="15" customHeight="1">
@@ -12417,7 +12444,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F325" s="7">
         <v>320</v>
@@ -12426,7 +12453,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H325" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="I325" s="7">
         <v>146</v>
@@ -12452,27 +12479,27 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -12487,7 +12514,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -12496,18 +12523,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
       <c t="s" r="M327" s="7">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="328" ht="14.25" customHeight="1">
@@ -12522,22 +12549,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12563,26 +12590,26 @@
         <v>13</v>
       </c>
       <c t="s" r="B330" s="7">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c t="s" r="C330" s="7">
         <v>68</v>
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G330" s="8">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c t="s" r="H330" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c t="s" r="J330" s="7">
         <v>76</v>
@@ -12607,7 +12634,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -12616,7 +12643,7 @@
         <v>28</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="I331" s="7">
         <v>152</v>
@@ -12642,13 +12669,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>28</v>
@@ -12662,7 +12689,7 @@
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
       <c t="s" r="M332" s="7">
-        <v>522</v>
+        <v>526</v>
       </c>
     </row>
     <row r="333" ht="14.25" customHeight="1">
@@ -12677,7 +12704,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -12692,12 +12719,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
       <c t="s" r="M333" s="7">
-        <v>523</v>
+        <v>527</v>
       </c>
     </row>
     <row r="334" ht="14.25" customHeight="1">
@@ -12712,7 +12739,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12724,17 +12751,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>110</v>
       </c>
       <c t="s" r="K334" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L334" s="7"/>
       <c t="s" r="M334" s="7">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="335" ht="15" customHeight="1">
@@ -12749,7 +12776,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
@@ -12758,10 +12785,10 @@
         <v>28</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>55</v>
@@ -12797,7 +12824,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F337" s="7">
         <v>320</v>
@@ -12809,15 +12836,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12832,7 +12859,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F338" s="7">
         <v>320</v>
@@ -12844,10 +12871,10 @@
         <v>28</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12867,7 +12894,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F339" s="7">
         <v>320</v>
@@ -12876,20 +12903,20 @@
         <v>28</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>41</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c t="s" r="K339" s="7">
         <v>130</v>
       </c>
       <c r="L339" s="7"/>
       <c t="s" r="M339" s="7">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="340" ht="15" customHeight="1">
@@ -12904,29 +12931,29 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F340" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>28</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>42</v>
       </c>
       <c t="s" r="K340" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="L340" s="7"/>
       <c t="s" r="M340" s="7">
-        <v>529</v>
+        <v>533</v>
       </c>
     </row>
     <row r="341" ht="14.25" customHeight="1">
@@ -12941,7 +12968,7 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F341" s="7">
         <v>320</v>
@@ -12956,12 +12983,12 @@
         <v>154</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
       <c t="s" r="M341" s="7">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="342" ht="14.25" customHeight="1">
@@ -12976,7 +13003,7 @@
       </c>
       <c r="D342" s="7"/>
       <c t="s" r="E342" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F342" s="7">
         <v>320</v>
@@ -12988,7 +13015,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>159</v>
@@ -12996,7 +13023,7 @@
       <c r="K342" s="7"/>
       <c r="L342" s="7"/>
       <c t="s" r="M342" s="7">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="343" ht="14.25" customHeight="1">
@@ -13011,7 +13038,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -13020,18 +13047,18 @@
         <v>28</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>533</v>
+        <v>537</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -13046,13 +13073,13 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c t="s" r="H344" s="8">
         <v>28</v>
@@ -13094,7 +13121,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -13109,12 +13136,12 @@
         <v>38</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
       <c t="s" r="M346" s="7">
-        <v>535</v>
+        <v>539</v>
       </c>
     </row>
     <row r="347" ht="14.25" customHeight="1">
@@ -13129,7 +13156,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -13141,17 +13168,17 @@
         <v>28</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c t="s" r="K347" s="7">
         <v>130</v>
       </c>
       <c r="L347" s="7"/>
       <c t="s" r="M347" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="348" ht="14.25" customHeight="1">
@@ -13166,7 +13193,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -13178,7 +13205,7 @@
         <v>75</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c t="s" r="J348" s="7">
         <v>81</v>
@@ -13186,7 +13213,7 @@
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
       <c t="s" r="M348" s="7">
-        <v>536</v>
+        <v>540</v>
       </c>
     </row>
     <row r="349" ht="14.25" customHeight="1">
@@ -13201,7 +13228,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -13213,7 +13240,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>102</v>
@@ -13221,7 +13248,7 @@
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
       <c t="s" r="M349" s="7">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="350" ht="15" customHeight="1">
@@ -13236,7 +13263,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -13256,7 +13283,7 @@
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
       <c t="s" r="M350" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="351" ht="14.25" customHeight="1">
@@ -13271,7 +13298,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -13321,27 +13348,27 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F353" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G353" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H353" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I353" s="7">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
       <c t="s" r="M353" s="7">
-        <v>539</v>
+        <v>543</v>
       </c>
     </row>
     <row r="354" ht="14.25" customHeight="1">
@@ -13356,7 +13383,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F354" s="7">
         <v>321</v>
@@ -13365,18 +13392,18 @@
         <v>17</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
       <c t="s" r="M354" s="7">
-        <v>540</v>
+        <v>544</v>
       </c>
     </row>
     <row r="355" ht="15" customHeight="1">
@@ -13391,13 +13418,13 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F355" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>62</v>
@@ -13411,7 +13438,7 @@
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
       <c t="s" r="M355" s="7">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="356" ht="14.25" customHeight="1">
@@ -13426,7 +13453,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F356" s="7">
         <v>321</v>
@@ -13435,17 +13462,19 @@
         <v>62</v>
       </c>
       <c t="s" r="H356" s="8">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c t="s" r="J356" s="7">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="K356" s="7"/>
       <c r="L356" s="7"/>
-      <c r="M356" s="7"/>
+      <c t="s" r="M356" s="7">
+        <v>482</v>
+      </c>
     </row>
     <row r="357" ht="14.25" customHeight="1">
       <c t="s" r="A357" s="6">
@@ -13459,22 +13488,22 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13507,13 +13536,13 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>100</v>
@@ -13522,12 +13551,12 @@
         <v>125</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
       <c t="s" r="M359" s="7">
-        <v>547</v>
+        <v>551</v>
       </c>
     </row>
     <row r="360" ht="15" customHeight="1">
@@ -13542,7 +13571,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F360" s="7">
         <v>321</v>
@@ -13562,7 +13591,7 @@
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
       <c t="s" r="M360" s="7">
-        <v>548</v>
+        <v>552</v>
       </c>
     </row>
     <row r="361" ht="14.25" customHeight="1">
@@ -13577,7 +13606,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
@@ -13589,7 +13618,7 @@
         <v>100</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J361" s="7">
         <v>154</v>
@@ -13597,7 +13626,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -13612,7 +13641,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -13621,10 +13650,10 @@
         <v>100</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="J362" s="7">
         <v>29</v>
@@ -13647,13 +13676,13 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>100</v>
@@ -13662,12 +13691,12 @@
         <v>104</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
       <c t="s" r="M363" s="7">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="364" ht="14.25" customHeight="1">
@@ -13697,7 +13726,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -13706,7 +13735,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H365" s="8">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="I365" s="7">
         <v>92</v>
@@ -13717,7 +13746,7 @@
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
       <c t="s" r="M365" s="7">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="366" ht="14.25" customHeight="1">
@@ -13732,13 +13761,13 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G366" s="8">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c t="s" r="H366" s="8">
         <v>62</v>
@@ -13747,12 +13776,12 @@
         <v>63</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>550</v>
+        <v>554</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13767,7 +13796,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -13776,7 +13805,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>26</v>
@@ -13802,19 +13831,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>85</v>
@@ -13822,7 +13851,7 @@
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
       <c t="s" r="M368" s="7">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="369" ht="14.25" customHeight="1">
@@ -13837,7 +13866,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -13846,17 +13875,19 @@
         <v>62</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
-      <c r="M369" s="7"/>
+      <c t="s" r="M369" s="7">
+        <v>557</v>
+      </c>
     </row>
     <row r="370" ht="15" customHeight="1">
       <c t="s" r="A370" s="6">
@@ -13870,22 +13901,22 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I370" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J370" s="7">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="K370" s="7"/>
       <c r="L370" s="7"/>
@@ -13918,7 +13949,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
@@ -13927,7 +13958,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>52</v>
@@ -13938,7 +13969,7 @@
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
       <c t="s" r="M372" s="7">
-        <v>555</v>
+        <v>560</v>
       </c>
     </row>
     <row r="373" ht="14.25" customHeight="1">
@@ -13953,13 +13984,13 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>62</v>
@@ -13968,12 +13999,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
       <c t="s" r="M373" s="7">
-        <v>556</v>
+        <v>561</v>
       </c>
     </row>
     <row r="374" ht="14.25" customHeight="1">
@@ -13988,7 +14019,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
@@ -13997,18 +14028,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H374" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J374" s="7">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K374" s="7"/>
       <c r="L374" s="7"/>
       <c t="s" r="M374" s="7">
-        <v>557</v>
+        <v>562</v>
       </c>
     </row>
     <row r="375" ht="15" customHeight="1">
@@ -14023,22 +14054,22 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G375" s="8">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c t="s" r="H375" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -14073,7 +14104,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -14082,18 +14113,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H377" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
       <c t="s" r="M377" s="7">
-        <v>559</v>
+        <v>564</v>
       </c>
     </row>
     <row r="378" ht="14.25" customHeight="1">
@@ -14108,13 +14139,13 @@
       </c>
       <c r="D378" s="7"/>
       <c t="s" r="E378" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F378" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G378" s="8">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="H378" s="8">
         <v>62</v>
@@ -14128,7 +14159,7 @@
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
       <c t="s" r="M378" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="379" ht="14.25" customHeight="1">
@@ -14143,7 +14174,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -14155,15 +14186,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
       <c t="s" r="M379" s="7">
-        <v>560</v>
+        <v>565</v>
       </c>
     </row>
     <row r="380" ht="15" customHeight="1">
@@ -14178,7 +14209,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -14190,7 +14221,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>25</v>
@@ -14213,7 +14244,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -14222,7 +14253,7 @@
         <v>62</v>
       </c>
       <c t="s" r="H381" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="I381" s="7">
         <v>119</v>
@@ -14248,27 +14279,27 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G382" s="8">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="H382" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
       <c t="s" r="M382" s="7">
-        <v>561</v>
+        <v>566</v>
       </c>
     </row>
     <row r="383" ht="14.25" customHeight="1">
@@ -14298,7 +14329,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="F384" s="7">
         <v>321</v>
@@ -14310,7 +14341,7 @@
         <v>143</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="J384" s="7">
         <v>43</v>
@@ -14318,7 +14349,7 @@
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -14333,7 +14364,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="F385" s="7">
         <v>321</v>
@@ -14348,7 +14379,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -14383,7 +14414,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -14395,15 +14426,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
       <c t="s" r="M387" s="7">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="388" ht="14.25" customHeight="1">
@@ -14418,7 +14449,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -14438,7 +14469,7 @@
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
       <c t="s" r="M388" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="389" ht="14.25" customHeight="1">
@@ -14453,7 +14484,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -14473,7 +14504,7 @@
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
       <c t="s" r="M389" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="390" ht="15" customHeight="1">
@@ -14488,7 +14519,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -14500,15 +14531,15 @@
         <v>62</v>
       </c>
       <c t="s" r="I390" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
       <c t="s" r="M390" s="7">
-        <v>564</v>
+        <v>569</v>
       </c>
     </row>
     <row r="391" ht="14.25" customHeight="1">
@@ -14523,7 +14554,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -14532,18 +14563,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c t="s" r="I391" s="7">
         <v>85</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14558,22 +14589,22 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>563</v>
+        <v>568</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>565</v>
+        <v>570</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -14606,7 +14637,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -14618,15 +14649,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
       <c t="s" r="M394" s="7">
-        <v>567</v>
+        <v>572</v>
       </c>
     </row>
     <row r="395" ht="15" customHeight="1">
@@ -14641,7 +14672,7 @@
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -14653,7 +14684,7 @@
         <v>148</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>23</v>
@@ -14661,7 +14692,7 @@
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
       <c t="s" r="M395" s="7">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="396" ht="14.25" customHeight="1">
@@ -14676,7 +14707,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
@@ -14688,15 +14719,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
       <c t="s" r="M396" s="7">
-        <v>568</v>
+        <v>573</v>
       </c>
     </row>
     <row r="397" ht="14.25" customHeight="1">
@@ -14726,7 +14757,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -14735,10 +14766,10 @@
         <v>75</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c t="s" r="J398" s="7">
         <v>56</v>
@@ -14746,7 +14777,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -14761,19 +14792,19 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>569</v>
+        <v>574</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>570</v>
+        <v>575</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>75</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>128</v>
@@ -14809,7 +14840,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14818,18 +14849,18 @@
         <v>75</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>573</v>
+        <v>578</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14844,13 +14875,13 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>572</v>
+        <v>577</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>75</v>
@@ -14859,12 +14890,12 @@
         <v>23</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>574</v>
+        <v>579</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
       <c t="s" r="M402" s="7">
-        <v>575</v>
+        <v>580</v>
       </c>
     </row>
     <row r="403" ht="14.25" customHeight="1">
@@ -14894,27 +14925,27 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c t="s" r="J404" s="7">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>578</v>
+        <v>583</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14929,7 +14960,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14941,7 +14972,7 @@
         <v>28</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J405" s="7">
         <v>48</v>
@@ -14949,7 +14980,7 @@
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
       <c t="s" r="M405" s="7">
-        <v>579</v>
+        <v>584</v>
       </c>
     </row>
     <row r="406" ht="14.25" customHeight="1">
@@ -14964,7 +14995,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="F406" s="7">
         <v>330</v>
@@ -14976,7 +15007,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I406" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J406" s="7">
         <v>110</v>
@@ -14984,7 +15015,7 @@
       <c r="K406" s="7"/>
       <c r="L406" s="7"/>
       <c t="s" r="M406" s="7">
-        <v>580</v>
+        <v>585</v>
       </c>
     </row>
     <row r="407" ht="14.25" customHeight="1">
@@ -15014,7 +15045,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -15034,7 +15065,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>582</v>
+        <v>587</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -15049,7 +15080,7 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
@@ -15058,18 +15089,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H409" s="8">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
       <c t="s" r="M409" s="7">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="410" ht="15" customHeight="1">
@@ -15084,27 +15115,27 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="F410" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G410" s="8">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c t="s" r="H410" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I410" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
       <c t="s" r="M410" s="7">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="411" ht="14.25" customHeight="1">
@@ -15134,7 +15165,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
@@ -15146,15 +15177,15 @@
         <v>28</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
       <c t="s" r="M412" s="7">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="413" ht="14.25" customHeight="1">
@@ -15169,7 +15200,7 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F413" s="7">
         <v>330</v>
@@ -15181,7 +15212,7 @@
         <v>62</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>45</v>
@@ -15189,7 +15220,7 @@
       <c r="K413" s="7"/>
       <c r="L413" s="7"/>
       <c t="s" r="M413" s="7">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="414" ht="14.25" customHeight="1">
@@ -15204,7 +15235,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -15219,7 +15250,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -15239,7 +15270,7 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
@@ -15248,18 +15279,18 @@
         <v>75</v>
       </c>
       <c t="s" r="H415" s="8">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c t="s" r="I415" s="7">
         <v>136</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
       <c t="s" r="M415" s="7">
-        <v>588</v>
+        <v>593</v>
       </c>
     </row>
     <row r="416" ht="14.25" customHeight="1">
@@ -15274,13 +15305,13 @@
       </c>
       <c r="D416" s="7"/>
       <c t="s" r="E416" s="7">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="F416" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G416" s="8">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c t="s" r="H416" s="8">
         <v>75</v>
@@ -15289,7 +15320,7 @@
         <v>78</v>
       </c>
       <c t="s" r="J416" s="7">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="K416" s="7"/>
       <c r="L416" s="7"/>
@@ -15322,29 +15353,29 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>590</v>
+        <v>595</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>583</v>
+        <v>588</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>62</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c t="s" r="K418" s="7">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L418" s="7"/>
       <c t="s" r="M418" s="7">
-        <v>592</v>
+        <v>597</v>
       </c>
     </row>
     <row r="419" ht="14.25" customHeight="1">
@@ -15374,7 +15405,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -15383,18 +15414,18 @@
         <v>62</v>
       </c>
       <c t="s" r="H420" s="8">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
       <c t="s" r="M420" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="421" ht="14.25" customHeight="1">
@@ -15409,13 +15440,13 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G421" s="8">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c t="s" r="H421" s="8">
         <v>62</v>
@@ -15424,17 +15455,17 @@
         <v>87</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
       <c t="s" r="M421" s="7">
-        <v>595</v>
+        <v>600</v>
       </c>
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c t="s" r="A422" s="9">
-        <v>596</v>
+        <v>601</v>
       </c>
       <c r="B422" s="9"/>
       <c r="C422" s="9"/>
@@ -15454,7 +15485,7 @@
     <row r="423" ht="65.25" customHeight="1"/>
     <row r="424" ht="16.5" customHeight="1">
       <c t="s" r="A424" s="10">
-        <v>597</v>
+        <v>602</v>
       </c>
       <c r="B424" s="10"/>
       <c r="C424" s="10"/>
@@ -15467,7 +15498,7 @@
       <c r="J424" s="10"/>
       <c r="K424" s="10"/>
       <c t="s" r="L424" s="11">
-        <v>598</v>
+        <v>603</v>
       </c>
       <c r="M424" s="11"/>
       <c r="N424" s="11"/>
